--- a/AQUAVO_FINAL_v9.xlsx
+++ b/AQUAVO_FINAL_v9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaafa\Desktop\upload\FishWebClean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9BD5D1-827F-4910-8AF9-677173D92730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F35309D-2EFB-40D5-94AA-92FE5EF25290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -329,7 +329,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="172" formatCode="_([$IQD]\ * #,##0.00_);_([$IQD]\ * \(#,##0.00\);_([$IQD]\ * &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_([$IQD]\ * #,##0.00_);_([$IQD]\ * \(#,##0.00\);_([$IQD]\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -504,16 +504,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
     <xf numFmtId="3" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
@@ -523,13 +513,13 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="172" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -553,13 +543,23 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="172" fontId="12" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -870,7 +870,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="49.28515625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="49.28515625" style="14" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="4" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
@@ -889,48 +889,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -989,56 +989,56 @@
       <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="7">
         <v>8</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="7">
         <v>2.48</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="7">
         <v>3768</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="7">
         <v>3177</v>
       </c>
-      <c r="H4" s="11">
-        <v>0</v>
-      </c>
-      <c r="I4" s="12">
+      <c r="H4" s="7">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8">
         <f>F4+G4</f>
         <v>6945</v>
       </c>
-      <c r="J4" s="13">
-        <v>9450</v>
-      </c>
-      <c r="K4" s="10">
+      <c r="J4" s="9">
+        <v>15000</v>
+      </c>
+      <c r="K4" s="6">
         <f>L4/J4</f>
-        <v>0.26507936507936508</v>
-      </c>
-      <c r="L4" s="14">
+        <v>0.53700000000000003</v>
+      </c>
+      <c r="L4" s="10">
         <f>J4-I4</f>
-        <v>2505</v>
-      </c>
-      <c r="M4" s="14">
-        <f>L4*D4</f>
-        <v>20040</v>
-      </c>
-      <c r="N4" s="11">
+        <v>8055</v>
+      </c>
+      <c r="M4" s="10">
+        <f t="shared" ref="M4:M11" si="0">L4*D4</f>
+        <v>64440</v>
+      </c>
+      <c r="N4" s="7">
         <v>16.600000000000001</v>
       </c>
-      <c r="O4" s="11">
+      <c r="O4" s="7">
         <v>11.9</v>
       </c>
-      <c r="P4" s="11">
+      <c r="P4" s="7">
         <v>9</v>
       </c>
-      <c r="Q4" s="11">
+      <c r="Q4" s="7">
         <v>650</v>
       </c>
     </row>
@@ -1046,56 +1046,56 @@
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="11">
         <v>8</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="11">
         <v>2.56</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="11">
         <v>3896</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="11">
         <v>3266</v>
       </c>
-      <c r="H5" s="15">
-        <v>0</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" ref="I5:I68" si="0">F5+G5</f>
+      <c r="H5" s="11">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8">
+        <f t="shared" ref="I5:I68" si="1">F5+G5</f>
         <v>7162</v>
       </c>
-      <c r="J5" s="13">
-        <v>10920</v>
-      </c>
-      <c r="K5" s="10">
-        <f t="shared" ref="K5:K68" si="1">L5/J5</f>
-        <v>0.34413919413919414</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" ref="L5:L68" si="2">J5-I5</f>
-        <v>3758</v>
-      </c>
-      <c r="M5" s="14">
-        <f>L5*D5</f>
-        <v>30064</v>
-      </c>
-      <c r="N5" s="15">
+      <c r="J5" s="9">
+        <v>15000</v>
+      </c>
+      <c r="K5" s="6">
+        <f t="shared" ref="K5:K68" si="2">L5/J5</f>
+        <v>0.52253333333333329</v>
+      </c>
+      <c r="L5" s="10">
+        <f t="shared" ref="L5:L68" si="3">J5-I5</f>
+        <v>7838</v>
+      </c>
+      <c r="M5" s="10">
+        <f t="shared" si="0"/>
+        <v>62704</v>
+      </c>
+      <c r="N5" s="11">
         <v>15.9</v>
       </c>
-      <c r="O5" s="15">
+      <c r="O5" s="11">
         <v>11.3</v>
       </c>
-      <c r="P5" s="15">
+      <c r="P5" s="11">
         <v>9</v>
       </c>
-      <c r="Q5" s="15">
+      <c r="Q5" s="11">
         <v>850</v>
       </c>
     </row>
@@ -1103,56 +1103,56 @@
       <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="11">
-        <v>8</v>
-      </c>
-      <c r="E6" s="11">
+      <c r="D6" s="7">
+        <v>7</v>
+      </c>
+      <c r="E6" s="7">
         <v>2.58</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="7">
         <v>3918</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="7">
         <v>3266</v>
       </c>
-      <c r="H6" s="11">
-        <v>0</v>
-      </c>
-      <c r="I6" s="12">
+      <c r="H6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8">
+        <f t="shared" si="1"/>
+        <v>7184</v>
+      </c>
+      <c r="J6" s="9">
+        <v>15000</v>
+      </c>
+      <c r="K6" s="6">
+        <f t="shared" si="2"/>
+        <v>0.52106666666666668</v>
+      </c>
+      <c r="L6" s="10">
+        <f t="shared" si="3"/>
+        <v>7816</v>
+      </c>
+      <c r="M6" s="10">
         <f t="shared" si="0"/>
-        <v>7184</v>
-      </c>
-      <c r="J6" s="13">
-        <v>11850</v>
-      </c>
-      <c r="K6" s="10">
-        <f t="shared" si="1"/>
-        <v>0.39375527426160339</v>
-      </c>
-      <c r="L6" s="14">
-        <f t="shared" si="2"/>
-        <v>4666</v>
-      </c>
-      <c r="M6" s="14">
-        <f>L6*D6</f>
-        <v>37328</v>
-      </c>
-      <c r="N6" s="11">
+        <v>54712</v>
+      </c>
+      <c r="N6" s="7">
         <v>16.100000000000001</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="7">
         <v>11.5</v>
       </c>
-      <c r="P6" s="11">
+      <c r="P6" s="7">
         <v>9</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="Q6" s="7">
         <v>900</v>
       </c>
     </row>
@@ -1160,56 +1160,56 @@
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="11">
         <v>1</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="11">
         <v>9.76</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="11">
         <v>14835</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="11">
         <v>3292</v>
       </c>
-      <c r="H7" s="15">
-        <v>0</v>
-      </c>
-      <c r="I7" s="12">
+      <c r="H7" s="11">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="1"/>
+        <v>18127</v>
+      </c>
+      <c r="J7" s="9">
+        <v>24850</v>
+      </c>
+      <c r="K7" s="6">
+        <f t="shared" si="2"/>
+        <v>0.27054325955734404</v>
+      </c>
+      <c r="L7" s="10">
+        <f t="shared" si="3"/>
+        <v>6723</v>
+      </c>
+      <c r="M7" s="10">
         <f t="shared" si="0"/>
-        <v>18127</v>
-      </c>
-      <c r="J7" s="13">
-        <v>24850</v>
-      </c>
-      <c r="K7" s="10">
-        <f t="shared" si="1"/>
-        <v>0.27054325955734404</v>
-      </c>
-      <c r="L7" s="14">
-        <f t="shared" si="2"/>
         <v>6723</v>
       </c>
-      <c r="M7" s="14">
-        <f>L7*D7</f>
-        <v>6723</v>
-      </c>
-      <c r="N7" s="15">
+      <c r="N7" s="11">
         <v>13.3</v>
       </c>
-      <c r="O7" s="15">
+      <c r="O7" s="11">
         <v>8.4</v>
       </c>
-      <c r="P7" s="15">
+      <c r="P7" s="11">
         <v>22</v>
       </c>
-      <c r="Q7" s="15">
+      <c r="Q7" s="11">
         <v>850</v>
       </c>
     </row>
@@ -1217,56 +1217,56 @@
       <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="7">
         <v>5</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="7">
         <v>3.52</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="7">
         <v>5352</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="7">
         <v>3248</v>
       </c>
-      <c r="H8" s="11">
-        <v>0</v>
-      </c>
-      <c r="I8" s="12">
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8">
+        <f t="shared" si="1"/>
+        <v>8600</v>
+      </c>
+      <c r="J8" s="9">
+        <v>14300</v>
+      </c>
+      <c r="K8" s="6">
+        <f t="shared" si="2"/>
+        <v>0.39860139860139859</v>
+      </c>
+      <c r="L8" s="10">
+        <f t="shared" si="3"/>
+        <v>5700</v>
+      </c>
+      <c r="M8" s="10">
         <f t="shared" si="0"/>
-        <v>8600</v>
-      </c>
-      <c r="J8" s="13">
-        <v>14300</v>
-      </c>
-      <c r="K8" s="10">
-        <f t="shared" si="1"/>
-        <v>0.39860139860139859</v>
-      </c>
-      <c r="L8" s="14">
-        <f t="shared" si="2"/>
-        <v>5700</v>
-      </c>
-      <c r="M8" s="14">
-        <f>L8*D8</f>
         <v>28500</v>
       </c>
-      <c r="N8" s="11">
+      <c r="N8" s="7">
         <v>13.3</v>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="7">
         <v>8.5</v>
       </c>
-      <c r="P8" s="11">
+      <c r="P8" s="7">
         <v>11</v>
       </c>
-      <c r="Q8" s="11">
+      <c r="Q8" s="7">
         <v>300</v>
       </c>
     </row>
@@ -1274,56 +1274,56 @@
       <c r="A9" s="3">
         <v>6</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="11">
         <v>3</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="11">
         <v>1.17</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="11">
         <v>1777</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="11">
         <v>3106</v>
       </c>
-      <c r="H9" s="15">
-        <v>0</v>
-      </c>
-      <c r="I9" s="12">
+      <c r="H9" s="11">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="1"/>
+        <v>4883</v>
+      </c>
+      <c r="J9" s="9">
+        <v>10600</v>
+      </c>
+      <c r="K9" s="6">
+        <f t="shared" si="2"/>
+        <v>0.53933962264150948</v>
+      </c>
+      <c r="L9" s="10">
+        <f t="shared" si="3"/>
+        <v>5717</v>
+      </c>
+      <c r="M9" s="10">
         <f t="shared" si="0"/>
-        <v>4883</v>
-      </c>
-      <c r="J9" s="13">
-        <v>10600</v>
-      </c>
-      <c r="K9" s="10">
-        <f t="shared" si="1"/>
-        <v>0.53933962264150948</v>
-      </c>
-      <c r="L9" s="14">
-        <f t="shared" si="2"/>
-        <v>5717</v>
-      </c>
-      <c r="M9" s="14">
-        <f>L9*D9</f>
         <v>17151</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="11">
         <v>31.6</v>
       </c>
-      <c r="O9" s="15">
+      <c r="O9" s="11">
         <v>27.8</v>
       </c>
-      <c r="P9" s="15">
+      <c r="P9" s="11">
         <v>8</v>
       </c>
-      <c r="Q9" s="15">
+      <c r="Q9" s="11">
         <v>600</v>
       </c>
     </row>
@@ -1331,56 +1331,56 @@
       <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="7">
         <v>15</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="7">
         <v>1.56</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="7">
         <v>2371</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="7">
         <v>3106</v>
       </c>
-      <c r="H10" s="11">
-        <v>0</v>
-      </c>
-      <c r="I10" s="12">
+      <c r="H10" s="7">
+        <v>0</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="1"/>
+        <v>5477</v>
+      </c>
+      <c r="J10" s="9">
+        <v>8450</v>
+      </c>
+      <c r="K10" s="6">
+        <f t="shared" si="2"/>
+        <v>0.35183431952662719</v>
+      </c>
+      <c r="L10" s="10">
+        <f t="shared" si="3"/>
+        <v>2973</v>
+      </c>
+      <c r="M10" s="10">
         <f t="shared" si="0"/>
-        <v>5477</v>
-      </c>
-      <c r="J10" s="13">
-        <v>8450</v>
-      </c>
-      <c r="K10" s="10">
-        <f t="shared" si="1"/>
-        <v>0.35183431952662719</v>
-      </c>
-      <c r="L10" s="14">
-        <f t="shared" si="2"/>
-        <v>2973</v>
-      </c>
-      <c r="M10" s="14">
-        <f>L10*D10</f>
         <v>44595</v>
       </c>
-      <c r="N10" s="11">
+      <c r="N10" s="7">
         <v>64.3</v>
       </c>
-      <c r="O10" s="11">
+      <c r="O10" s="7">
         <v>62.3</v>
       </c>
-      <c r="P10" s="11">
+      <c r="P10" s="7">
         <v>18</v>
       </c>
-      <c r="Q10" s="11">
+      <c r="Q10" s="7">
         <v>200</v>
       </c>
     </row>
@@ -1388,56 +1388,56 @@
       <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="11">
         <v>10</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="11">
         <v>0.37</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="11">
         <v>557</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="11">
         <v>3062</v>
       </c>
-      <c r="H11" s="15">
-        <v>0</v>
-      </c>
-      <c r="I11" s="12">
+      <c r="H11" s="11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="1"/>
+        <v>3619</v>
+      </c>
+      <c r="J11" s="9">
+        <v>6300</v>
+      </c>
+      <c r="K11" s="6">
+        <f t="shared" si="2"/>
+        <v>0.42555555555555558</v>
+      </c>
+      <c r="L11" s="10">
+        <f t="shared" si="3"/>
+        <v>2681</v>
+      </c>
+      <c r="M11" s="10">
         <f t="shared" si="0"/>
-        <v>3619</v>
-      </c>
-      <c r="J11" s="13">
-        <v>6300</v>
-      </c>
-      <c r="K11" s="10">
-        <f t="shared" si="1"/>
-        <v>0.42555555555555558</v>
-      </c>
-      <c r="L11" s="14">
-        <f t="shared" si="2"/>
-        <v>2681</v>
-      </c>
-      <c r="M11" s="14">
-        <f>L11*D11</f>
         <v>26810</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="11">
         <v>27.8</v>
       </c>
-      <c r="O11" s="15">
+      <c r="O11" s="11">
         <v>23.8</v>
       </c>
-      <c r="P11" s="15">
+      <c r="P11" s="11">
         <v>6</v>
       </c>
-      <c r="Q11" s="15">
+      <c r="Q11" s="11">
         <v>300</v>
       </c>
     </row>
@@ -1445,56 +1445,56 @@
       <c r="A12" s="2">
         <v>9</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="7">
         <v>10</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="7">
         <v>0.92</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="7">
         <v>1392</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="7">
         <v>3195</v>
       </c>
-      <c r="H12" s="11">
-        <v>0</v>
-      </c>
-      <c r="I12" s="12">
-        <f t="shared" si="0"/>
+      <c r="H12" s="7">
+        <v>0</v>
+      </c>
+      <c r="I12" s="8">
+        <f t="shared" si="1"/>
         <v>4587</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="9">
         <v>8300</v>
       </c>
-      <c r="K12" s="10">
-        <f t="shared" si="1"/>
+      <c r="K12" s="6">
+        <f t="shared" si="2"/>
         <v>0.44734939759036146</v>
       </c>
-      <c r="L12" s="14">
-        <f t="shared" si="2"/>
+      <c r="L12" s="10">
+        <f t="shared" si="3"/>
         <v>3713</v>
       </c>
-      <c r="M12" s="14">
-        <f t="shared" ref="M12:M69" si="3">L12*D12</f>
+      <c r="M12" s="10">
+        <f t="shared" ref="M12:M69" si="4">L12*D12</f>
         <v>37130</v>
       </c>
-      <c r="N12" s="11">
+      <c r="N12" s="7">
         <v>32.9</v>
       </c>
-      <c r="O12" s="11">
+      <c r="O12" s="7">
         <v>29.2</v>
       </c>
-      <c r="P12" s="11">
+      <c r="P12" s="7">
         <v>8</v>
       </c>
-      <c r="Q12" s="11">
+      <c r="Q12" s="7">
         <v>300</v>
       </c>
     </row>
@@ -1502,56 +1502,56 @@
       <c r="A13" s="3">
         <v>10</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="11">
         <v>5</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="11">
         <v>8.2799999999999994</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="11">
         <v>12588</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="11">
         <v>3780</v>
       </c>
-      <c r="H13" s="15">
-        <v>0</v>
-      </c>
-      <c r="I13" s="12">
-        <f t="shared" si="0"/>
+      <c r="H13" s="11">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="1"/>
         <v>16368</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="9">
         <v>27600</v>
       </c>
-      <c r="K13" s="10">
-        <f t="shared" si="1"/>
+      <c r="K13" s="6">
+        <f t="shared" si="2"/>
         <v>0.40695652173913044</v>
       </c>
-      <c r="L13" s="14">
-        <f t="shared" si="2"/>
+      <c r="L13" s="10">
+        <f t="shared" si="3"/>
         <v>11232</v>
       </c>
-      <c r="M13" s="14">
-        <f t="shared" si="3"/>
+      <c r="M13" s="10">
+        <f t="shared" si="4"/>
         <v>56160</v>
       </c>
-      <c r="N13" s="15">
+      <c r="N13" s="11">
         <v>27.9</v>
       </c>
-      <c r="O13" s="15">
+      <c r="O13" s="11">
         <v>23.9</v>
       </c>
-      <c r="P13" s="15">
+      <c r="P13" s="11">
         <v>25</v>
       </c>
-      <c r="Q13" s="15">
+      <c r="Q13" s="11">
         <v>350</v>
       </c>
     </row>
@@ -1559,56 +1559,56 @@
       <c r="A14" s="2">
         <v>11</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="7">
         <v>8</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="7">
         <v>2.68</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="7">
         <v>4068</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="7">
         <v>3168</v>
       </c>
-      <c r="H14" s="11">
-        <v>0</v>
-      </c>
-      <c r="I14" s="12">
-        <f t="shared" si="0"/>
+      <c r="H14" s="7">
+        <v>0</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="1"/>
         <v>7236</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="9">
         <v>11950</v>
       </c>
-      <c r="K14" s="10">
-        <f t="shared" si="1"/>
+      <c r="K14" s="6">
+        <f t="shared" si="2"/>
         <v>0.39447698744769877</v>
       </c>
-      <c r="L14" s="14">
-        <f t="shared" si="2"/>
+      <c r="L14" s="10">
+        <f t="shared" si="3"/>
         <v>4714</v>
       </c>
-      <c r="M14" s="14">
-        <f t="shared" si="3"/>
+      <c r="M14" s="10">
+        <f t="shared" si="4"/>
         <v>37712</v>
       </c>
-      <c r="N14" s="11">
+      <c r="N14" s="7">
         <v>30.1</v>
       </c>
-      <c r="O14" s="11">
+      <c r="O14" s="7">
         <v>26.2</v>
       </c>
-      <c r="P14" s="11">
+      <c r="P14" s="7">
         <v>11</v>
       </c>
-      <c r="Q14" s="11">
+      <c r="Q14" s="7">
         <v>950</v>
       </c>
     </row>
@@ -1616,56 +1616,56 @@
       <c r="A15" s="3">
         <v>12</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="11">
         <v>5</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="11">
         <v>0.99</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="11">
         <v>1505</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="11">
         <v>3168</v>
       </c>
-      <c r="H15" s="15">
-        <v>0</v>
-      </c>
-      <c r="I15" s="12">
-        <f t="shared" si="0"/>
+      <c r="H15" s="11">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="1"/>
         <v>4673</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="9">
         <v>8400</v>
       </c>
-      <c r="K15" s="10">
-        <f t="shared" si="1"/>
+      <c r="K15" s="6">
+        <f t="shared" si="2"/>
         <v>0.44369047619047619</v>
       </c>
-      <c r="L15" s="14">
-        <f t="shared" si="2"/>
+      <c r="L15" s="10">
+        <f t="shared" si="3"/>
         <v>3727</v>
       </c>
-      <c r="M15" s="14">
-        <f t="shared" si="3"/>
+      <c r="M15" s="10">
+        <f t="shared" si="4"/>
         <v>18635</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="11">
         <v>32.6</v>
       </c>
-      <c r="O15" s="15">
+      <c r="O15" s="11">
         <v>28.9</v>
       </c>
-      <c r="P15" s="15">
+      <c r="P15" s="11">
         <v>8</v>
       </c>
-      <c r="Q15" s="15">
+      <c r="Q15" s="11">
         <v>400</v>
       </c>
     </row>
@@ -1673,56 +1673,56 @@
       <c r="A16" s="2">
         <v>13</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="7">
         <v>4</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="7">
         <v>2.86</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="7">
         <v>4347</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="7">
         <v>3257</v>
       </c>
-      <c r="H16" s="11">
-        <v>0</v>
-      </c>
-      <c r="I16" s="12">
-        <f t="shared" si="0"/>
+      <c r="H16" s="7">
+        <v>0</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="1"/>
         <v>7604</v>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="9">
         <v>12300</v>
       </c>
-      <c r="K16" s="10">
-        <f t="shared" si="1"/>
+      <c r="K16" s="6">
+        <f t="shared" si="2"/>
         <v>0.38178861788617885</v>
       </c>
-      <c r="L16" s="14">
-        <f t="shared" si="2"/>
+      <c r="L16" s="10">
+        <f t="shared" si="3"/>
         <v>4696</v>
       </c>
-      <c r="M16" s="14">
-        <f t="shared" si="3"/>
+      <c r="M16" s="10">
+        <f t="shared" si="4"/>
         <v>18784</v>
       </c>
-      <c r="N16" s="11">
+      <c r="N16" s="7">
         <v>28.9</v>
       </c>
-      <c r="O16" s="11">
+      <c r="O16" s="7">
         <v>25</v>
       </c>
-      <c r="P16" s="11">
+      <c r="P16" s="7">
         <v>12</v>
       </c>
-      <c r="Q16" s="11">
+      <c r="Q16" s="7">
         <v>300</v>
       </c>
     </row>
@@ -1730,56 +1730,56 @@
       <c r="A17" s="3">
         <v>14</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="11">
         <v>4</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="11">
         <v>3.04</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="11">
         <v>4624</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="11">
         <v>3257</v>
       </c>
-      <c r="H17" s="15">
-        <v>0</v>
-      </c>
-      <c r="I17" s="12">
-        <f t="shared" si="0"/>
+      <c r="H17" s="11">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="1"/>
         <v>7881</v>
       </c>
-      <c r="J17" s="13">
+      <c r="J17" s="9">
         <v>12600</v>
       </c>
-      <c r="K17" s="10">
-        <f t="shared" si="1"/>
+      <c r="K17" s="6">
+        <f t="shared" si="2"/>
         <v>0.37452380952380954</v>
       </c>
-      <c r="L17" s="14">
-        <f t="shared" si="2"/>
+      <c r="L17" s="10">
+        <f t="shared" si="3"/>
         <v>4719</v>
       </c>
-      <c r="M17" s="14">
-        <f t="shared" si="3"/>
+      <c r="M17" s="10">
+        <f t="shared" si="4"/>
         <v>18876</v>
       </c>
-      <c r="N17" s="15">
+      <c r="N17" s="11">
         <v>28.3</v>
       </c>
-      <c r="O17" s="15">
+      <c r="O17" s="11">
         <v>24.3</v>
       </c>
-      <c r="P17" s="15">
+      <c r="P17" s="11">
         <v>12</v>
       </c>
-      <c r="Q17" s="15">
+      <c r="Q17" s="11">
         <v>600</v>
       </c>
     </row>
@@ -1787,56 +1787,56 @@
       <c r="A18" s="2">
         <v>15</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="7">
         <v>8</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="7">
         <v>1.31</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="7">
         <v>1991</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="7">
         <v>3611</v>
       </c>
-      <c r="H18" s="11">
-        <v>0</v>
-      </c>
-      <c r="I18" s="12">
-        <f t="shared" si="0"/>
+      <c r="H18" s="7">
+        <v>0</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="1"/>
         <v>5602</v>
       </c>
-      <c r="J18" s="13">
+      <c r="J18" s="9">
         <v>9600</v>
       </c>
-      <c r="K18" s="10">
-        <f t="shared" si="1"/>
+      <c r="K18" s="6">
+        <f t="shared" si="2"/>
         <v>0.41645833333333332</v>
       </c>
-      <c r="L18" s="14">
-        <f t="shared" si="2"/>
+      <c r="L18" s="10">
+        <f t="shared" si="3"/>
         <v>3998</v>
       </c>
-      <c r="M18" s="14">
-        <f t="shared" si="3"/>
+      <c r="M18" s="10">
+        <f t="shared" si="4"/>
         <v>31984</v>
       </c>
-      <c r="N18" s="11">
+      <c r="N18" s="7">
         <v>27.6</v>
       </c>
-      <c r="O18" s="11">
+      <c r="O18" s="7">
         <v>23.6</v>
       </c>
-      <c r="P18" s="11">
+      <c r="P18" s="7">
         <v>9</v>
       </c>
-      <c r="Q18" s="11">
+      <c r="Q18" s="7">
         <v>600</v>
       </c>
     </row>
@@ -1844,56 +1844,56 @@
       <c r="A19" s="3">
         <v>16</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="11">
         <v>5</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="11">
         <v>0.83</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="11">
         <v>1262</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="11">
         <v>3345</v>
       </c>
-      <c r="H19" s="15">
-        <v>0</v>
-      </c>
-      <c r="I19" s="12">
-        <f t="shared" si="0"/>
+      <c r="H19" s="11">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8">
+        <f t="shared" si="1"/>
         <v>4607</v>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="9">
         <v>7600</v>
       </c>
-      <c r="K19" s="10">
-        <f t="shared" si="1"/>
+      <c r="K19" s="6">
+        <f t="shared" si="2"/>
         <v>0.39381578947368423</v>
       </c>
-      <c r="L19" s="14">
-        <f t="shared" si="2"/>
+      <c r="L19" s="10">
+        <f t="shared" si="3"/>
         <v>2993</v>
       </c>
-      <c r="M19" s="14">
-        <f t="shared" si="3"/>
+      <c r="M19" s="10">
+        <f t="shared" si="4"/>
         <v>14965</v>
       </c>
-      <c r="N19" s="15">
+      <c r="N19" s="11">
         <v>31.3</v>
       </c>
-      <c r="O19" s="15">
+      <c r="O19" s="11">
         <v>27.5</v>
       </c>
-      <c r="P19" s="15">
+      <c r="P19" s="11">
         <v>8</v>
       </c>
-      <c r="Q19" s="15">
+      <c r="Q19" s="11">
         <v>600</v>
       </c>
     </row>
@@ -1901,56 +1901,56 @@
       <c r="A20" s="2">
         <v>17</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="7">
         <v>6</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="7">
         <v>1.67</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="7">
         <v>2538</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="7">
         <v>3514</v>
       </c>
-      <c r="H20" s="11">
-        <v>0</v>
-      </c>
-      <c r="I20" s="12">
-        <f t="shared" si="0"/>
+      <c r="H20" s="7">
+        <v>0</v>
+      </c>
+      <c r="I20" s="8">
+        <f t="shared" si="1"/>
         <v>6052</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J20" s="9">
         <v>11050</v>
       </c>
-      <c r="K20" s="10">
-        <f t="shared" si="1"/>
+      <c r="K20" s="6">
+        <f t="shared" si="2"/>
         <v>0.4523076923076923</v>
       </c>
-      <c r="L20" s="14">
-        <f t="shared" si="2"/>
+      <c r="L20" s="10">
+        <f t="shared" si="3"/>
         <v>4998</v>
       </c>
-      <c r="M20" s="14">
-        <f t="shared" si="3"/>
+      <c r="M20" s="10">
+        <f t="shared" si="4"/>
         <v>29988</v>
       </c>
-      <c r="N20" s="11">
+      <c r="N20" s="7">
         <v>32.799999999999997</v>
       </c>
-      <c r="O20" s="11">
+      <c r="O20" s="7">
         <v>29.1</v>
       </c>
-      <c r="P20" s="11">
+      <c r="P20" s="7">
         <v>11</v>
       </c>
-      <c r="Q20" s="11">
+      <c r="Q20" s="7">
         <v>50</v>
       </c>
     </row>
@@ -1958,56 +1958,56 @@
       <c r="A21" s="3">
         <v>18</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="11">
         <v>5</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="11">
         <v>2.61</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="11">
         <v>3961</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="11">
         <v>5207</v>
       </c>
-      <c r="H21" s="15">
-        <v>0</v>
-      </c>
-      <c r="I21" s="12">
-        <f t="shared" si="0"/>
+      <c r="H21" s="11">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="1"/>
         <v>9168</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="9">
         <v>15350</v>
       </c>
-      <c r="K21" s="10">
-        <f t="shared" si="1"/>
+      <c r="K21" s="6">
+        <f t="shared" si="2"/>
         <v>0.40273615635179155</v>
       </c>
-      <c r="L21" s="14">
-        <f t="shared" si="2"/>
+      <c r="L21" s="10">
+        <f t="shared" si="3"/>
         <v>6182</v>
       </c>
-      <c r="M21" s="14">
-        <f t="shared" si="3"/>
+      <c r="M21" s="10">
+        <f t="shared" si="4"/>
         <v>30910</v>
       </c>
-      <c r="N21" s="15">
+      <c r="N21" s="11">
         <v>28.9</v>
       </c>
-      <c r="O21" s="15">
+      <c r="O21" s="11">
         <v>24.9</v>
       </c>
-      <c r="P21" s="15">
+      <c r="P21" s="11">
         <v>15</v>
       </c>
-      <c r="Q21" s="15">
+      <c r="Q21" s="11">
         <v>350</v>
       </c>
     </row>
@@ -2015,56 +2015,56 @@
       <c r="A22" s="2">
         <v>19</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="7">
         <v>5</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="7">
         <v>0.97</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="7">
         <v>1477</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="7">
         <v>3523</v>
       </c>
-      <c r="H22" s="11">
-        <v>0</v>
-      </c>
-      <c r="I22" s="12">
-        <f t="shared" si="0"/>
+      <c r="H22" s="7">
+        <v>0</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="1"/>
         <v>5000</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="9">
         <v>9050</v>
       </c>
-      <c r="K22" s="10">
-        <f t="shared" si="1"/>
+      <c r="K22" s="6">
+        <f t="shared" si="2"/>
         <v>0.44751381215469616</v>
       </c>
-      <c r="L22" s="14">
-        <f t="shared" si="2"/>
+      <c r="L22" s="10">
+        <f t="shared" si="3"/>
         <v>4050</v>
       </c>
-      <c r="M22" s="14">
-        <f t="shared" si="3"/>
+      <c r="M22" s="10">
+        <f t="shared" si="4"/>
         <v>20250</v>
       </c>
-      <c r="N22" s="11">
+      <c r="N22" s="7">
         <v>30.2</v>
       </c>
-      <c r="O22" s="11">
+      <c r="O22" s="7">
         <v>26.3</v>
       </c>
-      <c r="P22" s="11">
+      <c r="P22" s="7">
         <v>9</v>
       </c>
-      <c r="Q22" s="11">
+      <c r="Q22" s="7">
         <v>50</v>
       </c>
     </row>
@@ -2072,56 +2072,56 @@
       <c r="A23" s="3">
         <v>20</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="11">
         <v>4</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="11">
         <v>2.61</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="11">
         <v>3967</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="11">
         <v>3168</v>
       </c>
-      <c r="H23" s="15">
-        <v>0</v>
-      </c>
-      <c r="I23" s="12">
-        <f t="shared" si="0"/>
+      <c r="H23" s="11">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="1"/>
         <v>7135</v>
       </c>
-      <c r="J23" s="13">
+      <c r="J23" s="9">
         <v>11850</v>
       </c>
-      <c r="K23" s="10">
-        <f t="shared" si="1"/>
+      <c r="K23" s="6">
+        <f t="shared" si="2"/>
         <v>0.39789029535864978</v>
       </c>
-      <c r="L23" s="14">
-        <f t="shared" si="2"/>
+      <c r="L23" s="10">
+        <f t="shared" si="3"/>
         <v>4715</v>
       </c>
-      <c r="M23" s="14">
-        <f t="shared" si="3"/>
+      <c r="M23" s="10">
+        <f t="shared" si="4"/>
         <v>18860</v>
       </c>
-      <c r="N23" s="15">
+      <c r="N23" s="11">
         <v>30.4</v>
       </c>
-      <c r="O23" s="15">
+      <c r="O23" s="11">
         <v>26.5</v>
       </c>
-      <c r="P23" s="15">
+      <c r="P23" s="11">
         <v>11</v>
       </c>
-      <c r="Q23" s="15">
+      <c r="Q23" s="11">
         <v>850</v>
       </c>
     </row>
@@ -2129,56 +2129,56 @@
       <c r="A24" s="2">
         <v>21</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="7">
         <v>4</v>
       </c>
-      <c r="E24" s="11">
-        <v>0</v>
-      </c>
-      <c r="F24" s="11">
-        <v>0</v>
-      </c>
-      <c r="G24" s="11">
+      <c r="E24" s="7">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7">
         <v>3230</v>
       </c>
-      <c r="H24" s="11">
-        <v>0</v>
-      </c>
-      <c r="I24" s="12">
-        <f t="shared" si="0"/>
+      <c r="H24" s="7">
+        <v>0</v>
+      </c>
+      <c r="I24" s="8">
+        <f t="shared" si="1"/>
         <v>3230</v>
       </c>
-      <c r="J24" s="13">
+      <c r="J24" s="9">
         <v>10850</v>
       </c>
-      <c r="K24" s="10">
-        <f t="shared" si="1"/>
+      <c r="K24" s="6">
+        <f t="shared" si="2"/>
         <v>0.70230414746543779</v>
       </c>
-      <c r="L24" s="14">
-        <f t="shared" si="2"/>
+      <c r="L24" s="10">
+        <f t="shared" si="3"/>
         <v>7620</v>
       </c>
-      <c r="M24" s="14">
-        <f t="shared" si="3"/>
+      <c r="M24" s="10">
+        <f t="shared" si="4"/>
         <v>30480</v>
       </c>
-      <c r="N24" s="11">
+      <c r="N24" s="7">
         <v>30.4</v>
       </c>
-      <c r="O24" s="11">
+      <c r="O24" s="7">
         <v>26.6</v>
       </c>
-      <c r="P24" s="11">
+      <c r="P24" s="7">
         <v>5</v>
       </c>
-      <c r="Q24" s="11">
+      <c r="Q24" s="7">
         <v>950</v>
       </c>
     </row>
@@ -2186,56 +2186,56 @@
       <c r="A25" s="3">
         <v>22</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="11">
         <v>3</v>
       </c>
-      <c r="E25" s="15">
-        <v>0</v>
-      </c>
-      <c r="F25" s="15">
-        <v>0</v>
-      </c>
-      <c r="G25" s="15">
+      <c r="E25" s="11">
+        <v>0</v>
+      </c>
+      <c r="F25" s="11">
+        <v>0</v>
+      </c>
+      <c r="G25" s="11">
         <v>3700</v>
       </c>
-      <c r="H25" s="15">
-        <v>0</v>
-      </c>
-      <c r="I25" s="12">
-        <f t="shared" si="0"/>
+      <c r="H25" s="11">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8">
+        <f t="shared" si="1"/>
         <v>3700</v>
       </c>
-      <c r="J25" s="13">
+      <c r="J25" s="9">
         <v>10650</v>
       </c>
-      <c r="K25" s="10">
-        <f t="shared" si="1"/>
+      <c r="K25" s="6">
+        <f t="shared" si="2"/>
         <v>0.65258215962441313</v>
       </c>
-      <c r="L25" s="14">
-        <f t="shared" si="2"/>
+      <c r="L25" s="10">
+        <f t="shared" si="3"/>
         <v>6950</v>
       </c>
-      <c r="M25" s="14">
-        <f t="shared" si="3"/>
+      <c r="M25" s="10">
+        <f t="shared" si="4"/>
         <v>20850</v>
       </c>
-      <c r="N25" s="15">
+      <c r="N25" s="11">
         <v>26.1</v>
       </c>
-      <c r="O25" s="15">
+      <c r="O25" s="11">
         <v>22</v>
       </c>
-      <c r="P25" s="15">
+      <c r="P25" s="11">
         <v>6</v>
       </c>
-      <c r="Q25" s="15">
+      <c r="Q25" s="11">
         <v>700</v>
       </c>
     </row>
@@ -2243,80 +2243,80 @@
       <c r="A26" s="2">
         <v>23</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>24</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="11">
         <v>2</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="11">
         <v>6.28</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="11">
         <v>9548</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="11">
         <v>8132</v>
       </c>
-      <c r="H27" s="24">
+      <c r="H27" s="20">
         <v>6188</v>
       </c>
-      <c r="I27" s="12">
+      <c r="I27" s="8">
         <f>F27+G27+H27</f>
         <v>23868</v>
       </c>
-      <c r="J27" s="22">
+      <c r="J27" s="18">
         <f>31500+H27</f>
         <v>37688</v>
       </c>
-      <c r="K27" s="10">
-        <f t="shared" si="1"/>
+      <c r="K27" s="6">
+        <f t="shared" si="2"/>
         <v>0.36669496922097217</v>
       </c>
-      <c r="L27" s="14">
-        <f t="shared" si="2"/>
+      <c r="L27" s="10">
+        <f t="shared" si="3"/>
         <v>13820</v>
       </c>
-      <c r="M27" s="14">
-        <f t="shared" si="3"/>
+      <c r="M27" s="10">
+        <f t="shared" si="4"/>
         <v>27640</v>
       </c>
-      <c r="N27" s="15">
+      <c r="N27" s="11">
         <v>22.2</v>
       </c>
-      <c r="O27" s="15">
+      <c r="O27" s="11">
         <v>17.899999999999999</v>
       </c>
-      <c r="P27" s="15">
+      <c r="P27" s="11">
         <v>30</v>
       </c>
-      <c r="Q27" s="15">
+      <c r="Q27" s="11">
         <v>550</v>
       </c>
     </row>
@@ -2324,57 +2324,57 @@
       <c r="A28" s="2">
         <v>25</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="7">
         <v>2</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="7">
         <v>9.73</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="7">
         <v>14793</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="7">
         <v>12565</v>
       </c>
-      <c r="H28" s="23">
+      <c r="H28" s="19">
         <v>8214</v>
       </c>
-      <c r="I28" s="12">
+      <c r="I28" s="8">
         <f>F28+G28+H28</f>
         <v>35572</v>
       </c>
-      <c r="J28" s="22">
+      <c r="J28" s="18">
         <f>(46250)+H28</f>
         <v>54464</v>
       </c>
-      <c r="K28" s="10">
-        <f t="shared" si="1"/>
+      <c r="K28" s="6">
+        <f t="shared" si="2"/>
         <v>0.34687132784958874</v>
       </c>
-      <c r="L28" s="14">
-        <f t="shared" si="2"/>
+      <c r="L28" s="10">
+        <f t="shared" si="3"/>
         <v>18892</v>
       </c>
-      <c r="M28" s="14">
-        <f t="shared" si="3"/>
+      <c r="M28" s="10">
+        <f t="shared" si="4"/>
         <v>37784</v>
       </c>
-      <c r="N28" s="11">
+      <c r="N28" s="7">
         <v>22</v>
       </c>
-      <c r="O28" s="11">
+      <c r="O28" s="7">
         <v>17.7</v>
       </c>
-      <c r="P28" s="11">
+      <c r="P28" s="7">
         <v>46</v>
       </c>
-      <c r="Q28" s="11">
+      <c r="Q28" s="7">
         <v>250</v>
       </c>
     </row>
@@ -2382,57 +2382,57 @@
       <c r="A29" s="3">
         <v>26</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="11">
         <v>2</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="11">
         <v>12.52</v>
       </c>
-      <c r="F29" s="15">
+      <c r="F29" s="11">
         <v>19032</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="11">
         <v>16288</v>
       </c>
-      <c r="H29" s="15">
+      <c r="H29" s="11">
         <v>7351</v>
       </c>
-      <c r="I29" s="12">
-        <f t="shared" ref="I28:I33" si="4">F29+G29+H29</f>
+      <c r="I29" s="8">
+        <f t="shared" ref="I29" si="5">F29+G29+H29</f>
         <v>42671</v>
       </c>
-      <c r="J29" s="22">
+      <c r="J29" s="18">
         <f>58580+H29</f>
         <v>65931</v>
       </c>
-      <c r="K29" s="10">
-        <f t="shared" si="1"/>
+      <c r="K29" s="6">
+        <f t="shared" si="2"/>
         <v>0.35279307154449346</v>
       </c>
-      <c r="L29" s="14">
-        <f t="shared" si="2"/>
+      <c r="L29" s="10">
+        <f t="shared" si="3"/>
         <v>23260</v>
       </c>
-      <c r="M29" s="14">
-        <f t="shared" si="3"/>
+      <c r="M29" s="10">
+        <f t="shared" si="4"/>
         <v>46520</v>
       </c>
-      <c r="N29" s="15">
+      <c r="N29" s="11">
         <v>21.5</v>
       </c>
-      <c r="O29" s="15">
+      <c r="O29" s="11">
         <v>17.2</v>
       </c>
-      <c r="P29" s="15">
+      <c r="P29" s="11">
         <v>58</v>
       </c>
-      <c r="Q29" s="15">
+      <c r="Q29" s="11">
         <v>850</v>
       </c>
     </row>
@@ -2440,57 +2440,57 @@
       <c r="A30" s="2">
         <v>27</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="7">
         <v>2</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="7">
         <v>8.59</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="7">
         <v>13059</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="7">
         <v>13097</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="7">
         <v>5044</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="8">
         <f>F30+G30+H30</f>
         <v>31200</v>
       </c>
-      <c r="J30" s="13">
+      <c r="J30" s="9">
         <f>43400+H30</f>
         <v>48444</v>
       </c>
-      <c r="K30" s="10">
-        <f t="shared" si="1"/>
+      <c r="K30" s="6">
+        <f t="shared" si="2"/>
         <v>0.35595739410453309</v>
       </c>
-      <c r="L30" s="14">
-        <f t="shared" si="2"/>
+      <c r="L30" s="10">
+        <f t="shared" si="3"/>
         <v>17244</v>
       </c>
-      <c r="M30" s="14">
-        <f t="shared" si="3"/>
+      <c r="M30" s="10">
+        <f t="shared" si="4"/>
         <v>34488</v>
       </c>
-      <c r="N30" s="11">
+      <c r="N30" s="7">
         <v>21.4</v>
       </c>
-      <c r="O30" s="11">
+      <c r="O30" s="7">
         <v>17</v>
       </c>
-      <c r="P30" s="11">
+      <c r="P30" s="7">
         <v>43</v>
       </c>
-      <c r="Q30" s="11">
+      <c r="Q30" s="7">
         <v>400</v>
       </c>
     </row>
@@ -2498,56 +2498,56 @@
       <c r="A31" s="3">
         <v>28</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="11">
         <v>2</v>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="11">
         <v>11.55</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="11">
         <v>17555</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="11">
         <v>16022</v>
       </c>
-      <c r="H31" s="15">
+      <c r="H31" s="11">
         <v>6781</v>
       </c>
-      <c r="I31" s="12">
+      <c r="I31" s="8">
         <f>F31+G31+H31</f>
         <v>40358</v>
       </c>
-      <c r="J31" s="13">
+      <c r="J31" s="9">
         <v>55550</v>
       </c>
-      <c r="K31" s="10">
-        <f t="shared" si="1"/>
+      <c r="K31" s="6">
+        <f t="shared" si="2"/>
         <v>0.27348334833483351</v>
       </c>
-      <c r="L31" s="14">
-        <f t="shared" si="2"/>
+      <c r="L31" s="10">
+        <f t="shared" si="3"/>
         <v>15192</v>
       </c>
-      <c r="M31" s="14">
-        <f t="shared" si="3"/>
+      <c r="M31" s="10">
+        <f t="shared" si="4"/>
         <v>30384</v>
       </c>
-      <c r="N31" s="15">
+      <c r="N31" s="11">
         <v>21.2</v>
       </c>
-      <c r="O31" s="15">
+      <c r="O31" s="11">
         <v>16.899999999999999</v>
       </c>
-      <c r="P31" s="15">
+      <c r="P31" s="11">
         <v>55</v>
       </c>
-      <c r="Q31" s="15">
+      <c r="Q31" s="11">
         <v>550</v>
       </c>
     </row>
@@ -2555,57 +2555,57 @@
       <c r="A32" s="2">
         <v>29</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="7">
         <v>2</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="7">
         <v>18.170000000000002</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="7">
         <v>27617</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="7">
         <v>20632</v>
       </c>
-      <c r="H32" s="11">
+      <c r="H32" s="7">
         <v>10667</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I32" s="8">
         <f>F32+G32+H32</f>
         <v>58916</v>
       </c>
-      <c r="J32" s="13">
+      <c r="J32" s="9">
         <f>81100+H32</f>
         <v>91767</v>
       </c>
-      <c r="K32" s="10">
-        <f t="shared" si="1"/>
+      <c r="K32" s="6">
+        <f t="shared" si="2"/>
         <v>0.35798271709873919</v>
       </c>
-      <c r="L32" s="14">
-        <f t="shared" si="2"/>
+      <c r="L32" s="10">
+        <f t="shared" si="3"/>
         <v>32851</v>
       </c>
-      <c r="M32" s="14">
-        <f t="shared" si="3"/>
+      <c r="M32" s="10">
+        <f t="shared" si="4"/>
         <v>65702</v>
       </c>
-      <c r="N32" s="11">
+      <c r="N32" s="7">
         <v>22</v>
       </c>
-      <c r="O32" s="11">
+      <c r="O32" s="7">
         <v>17.600000000000001</v>
       </c>
-      <c r="P32" s="11">
+      <c r="P32" s="7">
         <v>81</v>
       </c>
-      <c r="Q32" s="11">
+      <c r="Q32" s="7">
         <v>100</v>
       </c>
     </row>
@@ -2613,57 +2613,57 @@
       <c r="A33" s="3">
         <v>30</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C33" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="11">
         <v>2</v>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="11">
         <v>17.3</v>
       </c>
-      <c r="F33" s="15">
+      <c r="F33" s="11">
         <v>26290</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="11">
         <v>7902</v>
       </c>
-      <c r="H33" s="15">
+      <c r="H33" s="11">
         <v>5155</v>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="8">
         <f>F33+G33+H33</f>
         <v>39347</v>
       </c>
-      <c r="J33" s="13">
+      <c r="J33" s="9">
         <f>70550+H33</f>
         <v>75705</v>
       </c>
-      <c r="K33" s="10">
-        <f t="shared" si="1"/>
+      <c r="K33" s="6">
+        <f t="shared" si="2"/>
         <v>0.48025889967637542</v>
       </c>
-      <c r="L33" s="14">
-        <f t="shared" si="2"/>
+      <c r="L33" s="10">
+        <f t="shared" si="3"/>
         <v>36358</v>
       </c>
-      <c r="M33" s="14">
-        <f t="shared" si="3"/>
+      <c r="M33" s="10">
+        <f t="shared" si="4"/>
         <v>72716</v>
       </c>
-      <c r="N33" s="15">
+      <c r="N33" s="11">
         <v>22.1</v>
       </c>
-      <c r="O33" s="15">
+      <c r="O33" s="11">
         <v>17.8</v>
       </c>
-      <c r="P33" s="15">
+      <c r="P33" s="11">
         <v>61</v>
       </c>
-      <c r="Q33" s="15">
+      <c r="Q33" s="11">
         <v>550</v>
       </c>
     </row>
@@ -2671,56 +2671,56 @@
       <c r="A34" s="2">
         <v>31</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="21" t="s">
+      <c r="C34" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="7">
         <v>25</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="7">
         <v>0.63</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="7">
         <v>958</v>
       </c>
-      <c r="G34" s="11">
+      <c r="G34" s="7">
         <v>1648</v>
       </c>
-      <c r="H34" s="11">
-        <v>0</v>
-      </c>
-      <c r="I34" s="12">
-        <f t="shared" si="0"/>
+      <c r="H34" s="7">
+        <v>0</v>
+      </c>
+      <c r="I34" s="8">
+        <f t="shared" si="1"/>
         <v>2606</v>
       </c>
-      <c r="J34" s="13">
+      <c r="J34" s="9">
         <v>8300</v>
       </c>
-      <c r="K34" s="10">
-        <f t="shared" si="1"/>
+      <c r="K34" s="6">
+        <f t="shared" si="2"/>
         <v>0.68602409638554218</v>
       </c>
-      <c r="L34" s="14">
-        <f t="shared" si="2"/>
+      <c r="L34" s="10">
+        <f t="shared" si="3"/>
         <v>5694</v>
       </c>
-      <c r="M34" s="14">
-        <f t="shared" si="3"/>
+      <c r="M34" s="10">
+        <f t="shared" si="4"/>
         <v>142350</v>
       </c>
-      <c r="N34" s="11">
+      <c r="N34" s="7">
         <v>58</v>
       </c>
-      <c r="O34" s="11">
+      <c r="O34" s="7">
         <v>55.7</v>
       </c>
-      <c r="P34" s="11">
+      <c r="P34" s="7">
         <v>8</v>
       </c>
-      <c r="Q34" s="11">
+      <c r="Q34" s="7">
         <v>300</v>
       </c>
     </row>
@@ -2728,56 +2728,56 @@
       <c r="A35" s="3">
         <v>32</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="21" t="s">
+      <c r="C35" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="11">
         <v>15</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="11">
         <v>1.8</v>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="11">
         <v>2736</v>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="11">
         <v>2087</v>
       </c>
-      <c r="H35" s="15">
-        <v>0</v>
-      </c>
-      <c r="I35" s="12">
-        <f t="shared" si="0"/>
+      <c r="H35" s="11">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8">
+        <f t="shared" si="1"/>
         <v>4823</v>
       </c>
-      <c r="J35" s="13">
+      <c r="J35" s="9">
         <v>12550</v>
       </c>
-      <c r="K35" s="10">
-        <f t="shared" si="1"/>
+      <c r="K35" s="6">
+        <f t="shared" si="2"/>
         <v>0.61569721115537845</v>
       </c>
-      <c r="L35" s="14">
-        <f t="shared" si="2"/>
+      <c r="L35" s="10">
+        <f t="shared" si="3"/>
         <v>7727</v>
       </c>
-      <c r="M35" s="14">
-        <f t="shared" si="3"/>
+      <c r="M35" s="10">
+        <f t="shared" si="4"/>
         <v>115905</v>
       </c>
-      <c r="N35" s="15">
+      <c r="N35" s="11">
         <v>53.7</v>
       </c>
-      <c r="O35" s="15">
+      <c r="O35" s="11">
         <v>51.1</v>
       </c>
-      <c r="P35" s="15">
+      <c r="P35" s="11">
         <v>12</v>
       </c>
-      <c r="Q35" s="15">
+      <c r="Q35" s="11">
         <v>550</v>
       </c>
     </row>
@@ -2785,56 +2785,56 @@
       <c r="A36" s="2">
         <v>33</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="7">
         <v>20</v>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="7">
         <v>0.97</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="7">
         <v>1474</v>
       </c>
-      <c r="G36" s="11">
+      <c r="G36" s="7">
         <v>1729</v>
       </c>
-      <c r="H36" s="11">
-        <v>0</v>
-      </c>
-      <c r="I36" s="12">
-        <f t="shared" si="0"/>
+      <c r="H36" s="7">
+        <v>0</v>
+      </c>
+      <c r="I36" s="8">
+        <f t="shared" si="1"/>
         <v>3203</v>
       </c>
-      <c r="J36" s="13">
+      <c r="J36" s="9">
         <v>8900</v>
       </c>
-      <c r="K36" s="10">
-        <f t="shared" si="1"/>
+      <c r="K36" s="6">
+        <f t="shared" si="2"/>
         <v>0.64011235955056178</v>
       </c>
-      <c r="L36" s="14">
-        <f t="shared" si="2"/>
+      <c r="L36" s="10">
+        <f t="shared" si="3"/>
         <v>5697</v>
       </c>
-      <c r="M36" s="14">
-        <f t="shared" si="3"/>
+      <c r="M36" s="10">
+        <f t="shared" si="4"/>
         <v>113940</v>
       </c>
-      <c r="N36" s="11">
+      <c r="N36" s="7">
         <v>53.8</v>
       </c>
-      <c r="O36" s="11">
+      <c r="O36" s="7">
         <v>51.2</v>
       </c>
-      <c r="P36" s="11">
+      <c r="P36" s="7">
         <v>8</v>
       </c>
-      <c r="Q36" s="11">
+      <c r="Q36" s="7">
         <v>900</v>
       </c>
     </row>
@@ -2842,56 +2842,56 @@
       <c r="A37" s="3">
         <v>34</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="11">
         <v>30</v>
       </c>
-      <c r="E37" s="15">
+      <c r="E37" s="11">
         <v>1.35</v>
       </c>
-      <c r="F37" s="15">
+      <c r="F37" s="11">
         <v>2052</v>
       </c>
-      <c r="G37" s="15">
+      <c r="G37" s="11">
         <v>1713</v>
       </c>
-      <c r="H37" s="15">
-        <v>0</v>
-      </c>
-      <c r="I37" s="12">
-        <f t="shared" si="0"/>
+      <c r="H37" s="11">
+        <v>0</v>
+      </c>
+      <c r="I37" s="8">
+        <f t="shared" si="1"/>
         <v>3765</v>
       </c>
-      <c r="J37" s="13">
+      <c r="J37" s="9">
         <v>10450</v>
       </c>
-      <c r="K37" s="10">
-        <f t="shared" si="1"/>
+      <c r="K37" s="6">
+        <f t="shared" si="2"/>
         <v>0.63971291866028712</v>
       </c>
-      <c r="L37" s="14">
-        <f t="shared" si="2"/>
+      <c r="L37" s="10">
+        <f t="shared" si="3"/>
         <v>6685</v>
       </c>
-      <c r="M37" s="14">
-        <f t="shared" si="3"/>
+      <c r="M37" s="10">
+        <f t="shared" si="4"/>
         <v>200550</v>
       </c>
-      <c r="N37" s="15">
+      <c r="N37" s="11">
         <v>55</v>
       </c>
-      <c r="O37" s="15">
+      <c r="O37" s="11">
         <v>52.5</v>
       </c>
-      <c r="P37" s="15">
+      <c r="P37" s="11">
         <v>10</v>
       </c>
-      <c r="Q37" s="15">
+      <c r="Q37" s="11">
         <v>450</v>
       </c>
     </row>
@@ -2899,56 +2899,56 @@
       <c r="A38" s="2">
         <v>35</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="21" t="s">
+      <c r="C38" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="7">
         <v>5</v>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="7">
         <v>0.86</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="7">
         <v>1307</v>
       </c>
-      <c r="G38" s="11">
+      <c r="G38" s="7">
         <v>2087</v>
       </c>
-      <c r="H38" s="11">
-        <v>0</v>
-      </c>
-      <c r="I38" s="12">
-        <f t="shared" si="0"/>
+      <c r="H38" s="7">
+        <v>0</v>
+      </c>
+      <c r="I38" s="8">
+        <f t="shared" si="1"/>
         <v>3394</v>
       </c>
-      <c r="J38" s="13">
+      <c r="J38" s="9">
         <v>10100</v>
       </c>
-      <c r="K38" s="10">
-        <f t="shared" si="1"/>
+      <c r="K38" s="6">
+        <f t="shared" si="2"/>
         <v>0.66396039603960399</v>
       </c>
-      <c r="L38" s="14">
-        <f t="shared" si="2"/>
+      <c r="L38" s="10">
+        <f t="shared" si="3"/>
         <v>6706</v>
       </c>
-      <c r="M38" s="14">
-        <f t="shared" si="3"/>
+      <c r="M38" s="10">
+        <f t="shared" si="4"/>
         <v>33530</v>
       </c>
-      <c r="N38" s="11">
+      <c r="N38" s="7">
         <v>57.3</v>
       </c>
-      <c r="O38" s="11">
+      <c r="O38" s="7">
         <v>54.9</v>
       </c>
-      <c r="P38" s="11">
+      <c r="P38" s="7">
         <v>10</v>
       </c>
-      <c r="Q38" s="11">
+      <c r="Q38" s="7">
         <v>100</v>
       </c>
     </row>
@@ -2956,56 +2956,56 @@
       <c r="A39" s="3">
         <v>36</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="21" t="s">
+      <c r="C39" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="11">
         <v>6</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="11">
         <v>1.7</v>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="11">
         <v>2584</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="11">
         <v>1583</v>
       </c>
-      <c r="H39" s="15">
-        <v>0</v>
-      </c>
-      <c r="I39" s="12">
-        <f t="shared" si="0"/>
+      <c r="H39" s="11">
+        <v>0</v>
+      </c>
+      <c r="I39" s="8">
+        <f t="shared" si="1"/>
         <v>4167</v>
       </c>
-      <c r="J39" s="13">
+      <c r="J39" s="9">
         <v>10850</v>
       </c>
-      <c r="K39" s="10">
-        <f t="shared" si="1"/>
+      <c r="K39" s="6">
+        <f t="shared" si="2"/>
         <v>0.6159447004608295</v>
       </c>
-      <c r="L39" s="14">
-        <f t="shared" si="2"/>
+      <c r="L39" s="10">
+        <f t="shared" si="3"/>
         <v>6683</v>
       </c>
-      <c r="M39" s="14">
-        <f t="shared" si="3"/>
+      <c r="M39" s="10">
+        <f t="shared" si="4"/>
         <v>40098</v>
       </c>
-      <c r="N39" s="15">
+      <c r="N39" s="11">
         <v>52.8</v>
       </c>
-      <c r="O39" s="15">
+      <c r="O39" s="11">
         <v>50.1</v>
       </c>
-      <c r="P39" s="15">
+      <c r="P39" s="11">
         <v>10</v>
       </c>
-      <c r="Q39" s="15">
+      <c r="Q39" s="11">
         <v>850</v>
       </c>
     </row>
@@ -3013,56 +3013,56 @@
       <c r="A40" s="2">
         <v>37</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="21" t="s">
+      <c r="C40" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="7">
         <v>10</v>
       </c>
-      <c r="E40" s="11">
+      <c r="E40" s="7">
         <v>1.65</v>
       </c>
-      <c r="F40" s="11">
+      <c r="F40" s="7">
         <v>2508</v>
       </c>
-      <c r="G40" s="11">
+      <c r="G40" s="7">
         <v>1697</v>
       </c>
-      <c r="H40" s="11">
-        <v>0</v>
-      </c>
-      <c r="I40" s="12">
-        <f t="shared" si="0"/>
+      <c r="H40" s="7">
+        <v>0</v>
+      </c>
+      <c r="I40" s="8">
+        <f t="shared" si="1"/>
         <v>4205</v>
       </c>
-      <c r="J40" s="13">
+      <c r="J40" s="9">
         <v>11900</v>
       </c>
-      <c r="K40" s="10">
-        <f t="shared" si="1"/>
+      <c r="K40" s="6">
+        <f t="shared" si="2"/>
         <v>0.64663865546218491</v>
       </c>
-      <c r="L40" s="14">
-        <f t="shared" si="2"/>
+      <c r="L40" s="10">
+        <f t="shared" si="3"/>
         <v>7695</v>
       </c>
-      <c r="M40" s="14">
-        <f t="shared" si="3"/>
+      <c r="M40" s="10">
+        <f t="shared" si="4"/>
         <v>76950</v>
       </c>
-      <c r="N40" s="11">
+      <c r="N40" s="7">
         <v>56.6</v>
       </c>
-      <c r="O40" s="11">
+      <c r="O40" s="7">
         <v>54.2</v>
       </c>
-      <c r="P40" s="11">
+      <c r="P40" s="7">
         <v>11</v>
       </c>
-      <c r="Q40" s="11">
+      <c r="Q40" s="7">
         <v>900</v>
       </c>
     </row>
@@ -3070,56 +3070,56 @@
       <c r="A41" s="3">
         <v>38</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="11">
         <v>3</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="11">
         <v>1.27</v>
       </c>
-      <c r="F41" s="15">
+      <c r="F41" s="11">
         <v>1930</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="11">
         <v>1664</v>
       </c>
-      <c r="H41" s="15">
-        <v>0</v>
-      </c>
-      <c r="I41" s="12">
-        <f t="shared" si="0"/>
+      <c r="H41" s="11">
+        <v>0</v>
+      </c>
+      <c r="I41" s="8">
+        <f t="shared" si="1"/>
         <v>3594</v>
       </c>
-      <c r="J41" s="13">
+      <c r="J41" s="9">
         <v>10300</v>
       </c>
-      <c r="K41" s="10">
-        <f t="shared" si="1"/>
+      <c r="K41" s="6">
+        <f t="shared" si="2"/>
         <v>0.6510679611650485</v>
       </c>
-      <c r="L41" s="14">
-        <f t="shared" si="2"/>
+      <c r="L41" s="10">
+        <f t="shared" si="3"/>
         <v>6706</v>
       </c>
-      <c r="M41" s="14">
-        <f t="shared" si="3"/>
+      <c r="M41" s="10">
+        <f t="shared" si="4"/>
         <v>20118</v>
       </c>
-      <c r="N41" s="15">
+      <c r="N41" s="11">
         <v>56.1</v>
       </c>
-      <c r="O41" s="15">
+      <c r="O41" s="11">
         <v>53.6</v>
       </c>
-      <c r="P41" s="15">
+      <c r="P41" s="11">
         <v>10</v>
       </c>
-      <c r="Q41" s="15">
+      <c r="Q41" s="11">
         <v>300</v>
       </c>
     </row>
@@ -3127,56 +3127,56 @@
       <c r="A42" s="2">
         <v>39</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C42" s="21" t="s">
+      <c r="C42" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D42" s="7">
         <v>15</v>
       </c>
-      <c r="E42" s="11">
-        <v>0</v>
-      </c>
-      <c r="F42" s="11">
-        <v>0</v>
-      </c>
-      <c r="G42" s="11">
+      <c r="E42" s="7">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7">
+        <v>0</v>
+      </c>
+      <c r="G42" s="7">
         <v>1583</v>
       </c>
-      <c r="H42" s="11">
-        <v>0</v>
-      </c>
-      <c r="I42" s="12">
-        <f t="shared" si="0"/>
+      <c r="H42" s="7">
+        <v>0</v>
+      </c>
+      <c r="I42" s="8">
+        <f t="shared" si="1"/>
         <v>1583</v>
       </c>
-      <c r="J42" s="13">
+      <c r="J42" s="9">
         <v>5300</v>
       </c>
-      <c r="K42" s="10">
-        <f t="shared" si="1"/>
+      <c r="K42" s="6">
+        <f t="shared" si="2"/>
         <v>0.70132075471698119</v>
       </c>
-      <c r="L42" s="14">
-        <f t="shared" si="2"/>
+      <c r="L42" s="10">
+        <f t="shared" si="3"/>
         <v>3717</v>
       </c>
-      <c r="M42" s="14">
-        <f t="shared" si="3"/>
+      <c r="M42" s="10">
+        <f t="shared" si="4"/>
         <v>55755</v>
       </c>
-      <c r="N42" s="11">
+      <c r="N42" s="7">
         <v>54.6</v>
       </c>
-      <c r="O42" s="11">
+      <c r="O42" s="7">
         <v>52.1</v>
       </c>
-      <c r="P42" s="11">
+      <c r="P42" s="7">
         <v>5</v>
       </c>
-      <c r="Q42" s="11">
+      <c r="Q42" s="7">
         <v>300</v>
       </c>
     </row>
@@ -3184,56 +3184,56 @@
       <c r="A43" s="3">
         <v>40</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C43" s="21" t="s">
+      <c r="C43" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D43" s="15">
+      <c r="D43" s="11">
         <v>10</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="11">
         <v>1.04</v>
       </c>
-      <c r="F43" s="15">
+      <c r="F43" s="11">
         <v>1581</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="11">
         <v>1859</v>
       </c>
-      <c r="H43" s="15">
-        <v>0</v>
-      </c>
-      <c r="I43" s="12">
-        <f t="shared" si="0"/>
+      <c r="H43" s="11">
+        <v>0</v>
+      </c>
+      <c r="I43" s="8">
+        <f t="shared" si="1"/>
         <v>3440</v>
       </c>
-      <c r="J43" s="13">
+      <c r="J43" s="9">
         <v>10150</v>
       </c>
-      <c r="K43" s="10">
-        <f t="shared" si="1"/>
+      <c r="K43" s="6">
+        <f t="shared" si="2"/>
         <v>0.66108374384236457</v>
       </c>
-      <c r="L43" s="14">
-        <f t="shared" si="2"/>
+      <c r="L43" s="10">
+        <f t="shared" si="3"/>
         <v>6710</v>
       </c>
-      <c r="M43" s="14">
-        <f t="shared" si="3"/>
+      <c r="M43" s="10">
+        <f t="shared" si="4"/>
         <v>67100</v>
       </c>
-      <c r="N43" s="15">
+      <c r="N43" s="11">
         <v>57</v>
       </c>
-      <c r="O43" s="15">
+      <c r="O43" s="11">
         <v>54.6</v>
       </c>
-      <c r="P43" s="15">
+      <c r="P43" s="11">
         <v>10</v>
       </c>
-      <c r="Q43" s="15">
+      <c r="Q43" s="11">
         <v>150</v>
       </c>
     </row>
@@ -3241,56 +3241,56 @@
       <c r="A44" s="2">
         <v>41</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="21" t="s">
+      <c r="C44" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D44" s="11">
+      <c r="D44" s="7">
         <v>12</v>
       </c>
-      <c r="E44" s="11">
+      <c r="E44" s="7">
         <v>1.69</v>
       </c>
-      <c r="F44" s="11">
+      <c r="F44" s="7">
         <v>2569</v>
       </c>
-      <c r="G44" s="11">
+      <c r="G44" s="7">
         <v>2087</v>
       </c>
-      <c r="H44" s="11">
-        <v>0</v>
-      </c>
-      <c r="I44" s="12">
-        <f t="shared" si="0"/>
+      <c r="H44" s="7">
+        <v>0</v>
+      </c>
+      <c r="I44" s="8">
+        <f t="shared" si="1"/>
         <v>4656</v>
       </c>
-      <c r="J44" s="13">
+      <c r="J44" s="9">
         <v>12350</v>
       </c>
-      <c r="K44" s="10">
-        <f t="shared" si="1"/>
+      <c r="K44" s="6">
+        <f t="shared" si="2"/>
         <v>0.62299595141700403</v>
       </c>
-      <c r="L44" s="14">
-        <f t="shared" si="2"/>
+      <c r="L44" s="10">
+        <f t="shared" si="3"/>
         <v>7694</v>
       </c>
-      <c r="M44" s="14">
-        <f t="shared" si="3"/>
+      <c r="M44" s="10">
+        <f t="shared" si="4"/>
         <v>92328</v>
       </c>
-      <c r="N44" s="11">
+      <c r="N44" s="7">
         <v>54.3</v>
       </c>
-      <c r="O44" s="11">
+      <c r="O44" s="7">
         <v>51.8</v>
       </c>
-      <c r="P44" s="11">
+      <c r="P44" s="7">
         <v>12</v>
       </c>
-      <c r="Q44" s="11">
+      <c r="Q44" s="7">
         <v>350</v>
       </c>
     </row>
@@ -3298,56 +3298,56 @@
       <c r="A45" s="3">
         <v>42</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c r="B45" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="21" t="s">
+      <c r="C45" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="15">
+      <c r="D45" s="11">
         <v>8</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="11">
         <v>0.9</v>
       </c>
-      <c r="F45" s="15">
+      <c r="F45" s="11">
         <v>1368</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="11">
         <v>1583</v>
       </c>
-      <c r="H45" s="15">
-        <v>0</v>
-      </c>
-      <c r="I45" s="12">
-        <f t="shared" si="0"/>
+      <c r="H45" s="11">
+        <v>0</v>
+      </c>
+      <c r="I45" s="8">
+        <f t="shared" si="1"/>
         <v>2951</v>
       </c>
-      <c r="J45" s="13">
+      <c r="J45" s="9">
         <v>8650</v>
       </c>
-      <c r="K45" s="10">
-        <f t="shared" si="1"/>
+      <c r="K45" s="6">
+        <f t="shared" si="2"/>
         <v>0.65884393063583813</v>
       </c>
-      <c r="L45" s="14">
-        <f t="shared" si="2"/>
+      <c r="L45" s="10">
+        <f t="shared" si="3"/>
         <v>5699</v>
       </c>
-      <c r="M45" s="14">
-        <f t="shared" si="3"/>
+      <c r="M45" s="10">
+        <f t="shared" si="4"/>
         <v>45592</v>
       </c>
-      <c r="N45" s="15">
+      <c r="N45" s="11">
         <v>55.5</v>
       </c>
-      <c r="O45" s="15">
+      <c r="O45" s="11">
         <v>53.1</v>
       </c>
-      <c r="P45" s="15">
+      <c r="P45" s="11">
         <v>8</v>
       </c>
-      <c r="Q45" s="15">
+      <c r="Q45" s="11">
         <v>650</v>
       </c>
     </row>
@@ -3355,56 +3355,56 @@
       <c r="A46" s="2">
         <v>43</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="21" t="s">
+      <c r="C46" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="7">
         <v>10</v>
       </c>
-      <c r="E46" s="11">
+      <c r="E46" s="7">
         <v>0.48</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F46" s="7">
         <v>730</v>
       </c>
-      <c r="G46" s="11">
+      <c r="G46" s="7">
         <v>1551</v>
       </c>
-      <c r="H46" s="11">
-        <v>0</v>
-      </c>
-      <c r="I46" s="12">
-        <f t="shared" si="0"/>
+      <c r="H46" s="7">
+        <v>0</v>
+      </c>
+      <c r="I46" s="8">
+        <f t="shared" si="1"/>
         <v>2281</v>
       </c>
-      <c r="J46" s="13">
+      <c r="J46" s="9">
         <v>5950</v>
       </c>
-      <c r="K46" s="10">
-        <f t="shared" si="1"/>
+      <c r="K46" s="6">
+        <f t="shared" si="2"/>
         <v>0.61663865546218488</v>
       </c>
-      <c r="L46" s="14">
-        <f t="shared" si="2"/>
+      <c r="L46" s="10">
+        <f t="shared" si="3"/>
         <v>3669</v>
       </c>
-      <c r="M46" s="14">
-        <f t="shared" si="3"/>
+      <c r="M46" s="10">
+        <f t="shared" si="4"/>
         <v>36690</v>
       </c>
-      <c r="N46" s="11">
+      <c r="N46" s="7">
         <v>54.8</v>
       </c>
-      <c r="O46" s="11">
+      <c r="O46" s="7">
         <v>52.3</v>
       </c>
-      <c r="P46" s="11">
+      <c r="P46" s="7">
         <v>6</v>
       </c>
-      <c r="Q46" s="11">
+      <c r="Q46" s="7">
         <v>950</v>
       </c>
     </row>
@@ -3412,56 +3412,56 @@
       <c r="A47" s="3">
         <v>44</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C47" s="21" t="s">
+      <c r="C47" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D47" s="15">
+      <c r="D47" s="11">
         <v>10</v>
       </c>
-      <c r="E47" s="15">
+      <c r="E47" s="11">
         <v>0.72</v>
       </c>
-      <c r="F47" s="15">
+      <c r="F47" s="11">
         <v>1092</v>
       </c>
-      <c r="G47" s="15">
+      <c r="G47" s="11">
         <v>2054</v>
       </c>
-      <c r="H47" s="15">
-        <v>0</v>
-      </c>
-      <c r="I47" s="12">
-        <f t="shared" si="0"/>
+      <c r="H47" s="11">
+        <v>0</v>
+      </c>
+      <c r="I47" s="8">
+        <f t="shared" si="1"/>
         <v>3146</v>
       </c>
-      <c r="J47" s="13">
+      <c r="J47" s="9">
         <v>12850</v>
       </c>
-      <c r="K47" s="10">
-        <f t="shared" si="1"/>
+      <c r="K47" s="6">
+        <f t="shared" si="2"/>
         <v>0.75517509727626464</v>
       </c>
-      <c r="L47" s="14">
-        <f t="shared" si="2"/>
+      <c r="L47" s="10">
+        <f t="shared" si="3"/>
         <v>9704</v>
       </c>
-      <c r="M47" s="14">
-        <f t="shared" si="3"/>
+      <c r="M47" s="10">
+        <f t="shared" si="4"/>
         <v>97040</v>
       </c>
-      <c r="N47" s="15">
+      <c r="N47" s="11">
         <v>68.5</v>
       </c>
-      <c r="O47" s="15">
+      <c r="O47" s="11">
         <v>66.7</v>
       </c>
-      <c r="P47" s="15">
+      <c r="P47" s="11">
         <v>12</v>
       </c>
-      <c r="Q47" s="15">
+      <c r="Q47" s="11">
         <v>850</v>
       </c>
     </row>
@@ -3469,56 +3469,56 @@
       <c r="A48" s="2">
         <v>45</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C48" s="21" t="s">
+      <c r="C48" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="7">
         <v>8</v>
       </c>
-      <c r="E48" s="11">
+      <c r="E48" s="7">
         <v>0.93</v>
       </c>
-      <c r="F48" s="11">
+      <c r="F48" s="7">
         <v>1414</v>
       </c>
-      <c r="G48" s="11">
+      <c r="G48" s="7">
         <v>2590</v>
       </c>
-      <c r="H48" s="11">
-        <v>0</v>
-      </c>
-      <c r="I48" s="12">
-        <f t="shared" si="0"/>
+      <c r="H48" s="7">
+        <v>0</v>
+      </c>
+      <c r="I48" s="8">
+        <f t="shared" si="1"/>
         <v>4004</v>
       </c>
-      <c r="J48" s="13">
+      <c r="J48" s="9">
         <v>17050</v>
       </c>
-      <c r="K48" s="10">
-        <f t="shared" si="1"/>
+      <c r="K48" s="6">
+        <f t="shared" si="2"/>
         <v>0.76516129032258062</v>
       </c>
-      <c r="L48" s="14">
-        <f t="shared" si="2"/>
+      <c r="L48" s="10">
+        <f t="shared" si="3"/>
         <v>13046</v>
       </c>
-      <c r="M48" s="14">
-        <f t="shared" si="3"/>
+      <c r="M48" s="10">
+        <f t="shared" si="4"/>
         <v>104368</v>
       </c>
-      <c r="N48" s="11">
+      <c r="N48" s="7">
         <v>69.099999999999994</v>
       </c>
-      <c r="O48" s="11">
+      <c r="O48" s="7">
         <v>67.400000000000006</v>
       </c>
-      <c r="P48" s="11">
+      <c r="P48" s="7">
         <v>17</v>
       </c>
-      <c r="Q48" s="11">
+      <c r="Q48" s="7">
         <v>50</v>
       </c>
     </row>
@@ -3526,56 +3526,56 @@
       <c r="A49" s="3">
         <v>46</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C49" s="21" t="s">
+      <c r="C49" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="15">
+      <c r="D49" s="11">
         <v>6</v>
       </c>
-      <c r="E49" s="15">
+      <c r="E49" s="11">
         <v>1.1299999999999999</v>
       </c>
-      <c r="F49" s="15">
+      <c r="F49" s="11">
         <v>1718</v>
       </c>
-      <c r="G49" s="15">
+      <c r="G49" s="11">
         <v>1583</v>
       </c>
-      <c r="H49" s="15">
-        <v>0</v>
-      </c>
-      <c r="I49" s="12">
-        <f t="shared" si="0"/>
+      <c r="H49" s="11">
+        <v>0</v>
+      </c>
+      <c r="I49" s="8">
+        <f t="shared" si="1"/>
         <v>3301</v>
       </c>
-      <c r="J49" s="13">
+      <c r="J49" s="9">
         <v>14050</v>
       </c>
-      <c r="K49" s="10">
-        <f t="shared" si="1"/>
+      <c r="K49" s="6">
+        <f t="shared" si="2"/>
         <v>0.76505338078291818</v>
       </c>
-      <c r="L49" s="14">
-        <f t="shared" si="2"/>
+      <c r="L49" s="10">
+        <f t="shared" si="3"/>
         <v>10749</v>
       </c>
-      <c r="M49" s="14">
-        <f t="shared" si="3"/>
+      <c r="M49" s="10">
+        <f t="shared" si="4"/>
         <v>64494</v>
       </c>
-      <c r="N49" s="15">
+      <c r="N49" s="11">
         <v>70</v>
       </c>
-      <c r="O49" s="15">
+      <c r="O49" s="11">
         <v>68.3</v>
       </c>
-      <c r="P49" s="15">
+      <c r="P49" s="11">
         <v>14</v>
       </c>
-      <c r="Q49" s="15">
+      <c r="Q49" s="11">
         <v>50</v>
       </c>
     </row>
@@ -3583,56 +3583,56 @@
       <c r="A50" s="2">
         <v>47</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C50" s="21" t="s">
+      <c r="C50" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D50" s="11">
+      <c r="D50" s="7">
         <v>10</v>
       </c>
-      <c r="E50" s="11">
+      <c r="E50" s="7">
         <v>2.34</v>
       </c>
-      <c r="F50" s="11">
+      <c r="F50" s="7">
         <v>3557</v>
       </c>
-      <c r="G50" s="11">
+      <c r="G50" s="7">
         <v>2899</v>
       </c>
-      <c r="H50" s="11">
-        <v>0</v>
-      </c>
-      <c r="I50" s="12">
-        <f t="shared" si="0"/>
+      <c r="H50" s="7">
+        <v>0</v>
+      </c>
+      <c r="I50" s="8">
+        <f t="shared" si="1"/>
         <v>6456</v>
       </c>
-      <c r="J50" s="13">
+      <c r="J50" s="9">
         <v>16450</v>
       </c>
-      <c r="K50" s="10">
-        <f t="shared" si="1"/>
+      <c r="K50" s="6">
+        <f t="shared" si="2"/>
         <v>0.60753799392097263</v>
       </c>
-      <c r="L50" s="14">
-        <f t="shared" si="2"/>
+      <c r="L50" s="10">
+        <f t="shared" si="3"/>
         <v>9994</v>
       </c>
-      <c r="M50" s="14">
-        <f t="shared" si="3"/>
+      <c r="M50" s="10">
+        <f t="shared" si="4"/>
         <v>99940</v>
       </c>
-      <c r="N50" s="11">
+      <c r="N50" s="7">
         <v>55</v>
       </c>
-      <c r="O50" s="11">
+      <c r="O50" s="7">
         <v>52.5</v>
       </c>
-      <c r="P50" s="11">
+      <c r="P50" s="7">
         <v>17</v>
       </c>
-      <c r="Q50" s="11">
+      <c r="Q50" s="7">
         <v>450</v>
       </c>
     </row>
@@ -3640,56 +3640,56 @@
       <c r="A51" s="3">
         <v>48</v>
       </c>
-      <c r="B51" s="20" t="s">
+      <c r="B51" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="C51" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="11">
         <v>5</v>
       </c>
-      <c r="E51" s="15">
+      <c r="E51" s="11">
         <v>1.38</v>
       </c>
-      <c r="F51" s="15">
+      <c r="F51" s="11">
         <v>2098</v>
       </c>
-      <c r="G51" s="15">
+      <c r="G51" s="11">
         <v>2363</v>
       </c>
-      <c r="H51" s="15">
-        <v>0</v>
-      </c>
-      <c r="I51" s="12">
-        <f t="shared" si="0"/>
+      <c r="H51" s="11">
+        <v>0</v>
+      </c>
+      <c r="I51" s="8">
+        <f t="shared" si="1"/>
         <v>4461</v>
       </c>
-      <c r="J51" s="13">
+      <c r="J51" s="9">
         <v>12450</v>
       </c>
-      <c r="K51" s="10">
-        <f t="shared" si="1"/>
+      <c r="K51" s="6">
+        <f t="shared" si="2"/>
         <v>0.64168674698795181</v>
       </c>
-      <c r="L51" s="14">
-        <f t="shared" si="2"/>
+      <c r="L51" s="10">
+        <f t="shared" si="3"/>
         <v>7989</v>
       </c>
-      <c r="M51" s="14">
-        <f t="shared" si="3"/>
+      <c r="M51" s="10">
+        <f t="shared" si="4"/>
         <v>39945</v>
       </c>
-      <c r="N51" s="15">
+      <c r="N51" s="11">
         <v>53.8</v>
       </c>
-      <c r="O51" s="15">
+      <c r="O51" s="11">
         <v>51.2</v>
       </c>
-      <c r="P51" s="15">
+      <c r="P51" s="11">
         <v>12</v>
       </c>
-      <c r="Q51" s="15">
+      <c r="Q51" s="11">
         <v>450</v>
       </c>
     </row>
@@ -3697,56 +3697,56 @@
       <c r="A52" s="2">
         <v>49</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C52" s="21" t="s">
+      <c r="C52" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="7">
         <v>15</v>
       </c>
-      <c r="E52" s="11">
+      <c r="E52" s="7">
         <v>0.72</v>
       </c>
-      <c r="F52" s="11">
+      <c r="F52" s="7">
         <v>1094</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G52" s="7">
         <v>2493</v>
       </c>
-      <c r="H52" s="11">
-        <v>0</v>
-      </c>
-      <c r="I52" s="12">
-        <f t="shared" si="0"/>
+      <c r="H52" s="7">
+        <v>0</v>
+      </c>
+      <c r="I52" s="8">
+        <f t="shared" si="1"/>
         <v>3587</v>
       </c>
-      <c r="J52" s="13">
+      <c r="J52" s="9">
         <v>6600</v>
       </c>
-      <c r="K52" s="10">
-        <f t="shared" si="1"/>
+      <c r="K52" s="6">
+        <f t="shared" si="2"/>
         <v>0.45651515151515154</v>
       </c>
-      <c r="L52" s="14">
-        <f t="shared" si="2"/>
+      <c r="L52" s="10">
+        <f t="shared" si="3"/>
         <v>3013</v>
       </c>
-      <c r="M52" s="14">
-        <f t="shared" si="3"/>
+      <c r="M52" s="10">
+        <f t="shared" si="4"/>
         <v>45195</v>
       </c>
-      <c r="N52" s="11">
+      <c r="N52" s="7">
         <v>54.4</v>
       </c>
-      <c r="O52" s="11">
+      <c r="O52" s="7">
         <v>51.9</v>
       </c>
-      <c r="P52" s="11">
+      <c r="P52" s="7">
         <v>10</v>
       </c>
-      <c r="Q52" s="11">
+      <c r="Q52" s="7">
         <v>600</v>
       </c>
     </row>
@@ -3754,56 +3754,56 @@
       <c r="A53" s="3">
         <v>50</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B53" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C53" s="21" t="s">
+      <c r="C53" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D53" s="15">
+      <c r="D53" s="11">
         <v>8</v>
       </c>
-      <c r="E53" s="15">
+      <c r="E53" s="11">
         <v>0.92</v>
       </c>
-      <c r="F53" s="15">
+      <c r="F53" s="11">
         <v>1392</v>
       </c>
-      <c r="G53" s="15">
+      <c r="G53" s="11">
         <v>2477</v>
       </c>
-      <c r="H53" s="15">
-        <v>0</v>
-      </c>
-      <c r="I53" s="12">
-        <f t="shared" si="0"/>
+      <c r="H53" s="11">
+        <v>0</v>
+      </c>
+      <c r="I53" s="8">
+        <f t="shared" si="1"/>
         <v>3869</v>
       </c>
-      <c r="J53" s="13">
+      <c r="J53" s="9">
         <v>10850</v>
       </c>
-      <c r="K53" s="10">
-        <f t="shared" si="1"/>
+      <c r="K53" s="6">
+        <f t="shared" si="2"/>
         <v>0.64341013824884796</v>
       </c>
-      <c r="L53" s="14">
-        <f t="shared" si="2"/>
+      <c r="L53" s="10">
+        <f t="shared" si="3"/>
         <v>6981</v>
       </c>
-      <c r="M53" s="14">
-        <f t="shared" si="3"/>
+      <c r="M53" s="10">
+        <f t="shared" si="4"/>
         <v>55848</v>
       </c>
-      <c r="N53" s="15">
+      <c r="N53" s="11">
         <v>52.7</v>
       </c>
-      <c r="O53" s="15">
+      <c r="O53" s="11">
         <v>50.1</v>
       </c>
-      <c r="P53" s="15">
+      <c r="P53" s="11">
         <v>10</v>
       </c>
-      <c r="Q53" s="15">
+      <c r="Q53" s="11">
         <v>850</v>
       </c>
     </row>
@@ -3811,56 +3811,56 @@
       <c r="A54" s="2">
         <v>51</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C54" s="21" t="s">
+      <c r="C54" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="7">
         <v>8</v>
       </c>
-      <c r="E54" s="11">
+      <c r="E54" s="7">
         <v>2.87</v>
       </c>
-      <c r="F54" s="11">
+      <c r="F54" s="7">
         <v>4362</v>
       </c>
-      <c r="G54" s="11">
+      <c r="G54" s="7">
         <v>2330</v>
       </c>
-      <c r="H54" s="11">
-        <v>0</v>
-      </c>
-      <c r="I54" s="12">
-        <f t="shared" si="0"/>
+      <c r="H54" s="7">
+        <v>0</v>
+      </c>
+      <c r="I54" s="8">
+        <f t="shared" si="1"/>
         <v>6692</v>
       </c>
-      <c r="J54" s="13">
+      <c r="J54" s="9">
         <v>15770</v>
       </c>
-      <c r="K54" s="10">
-        <f t="shared" si="1"/>
+      <c r="K54" s="6">
+        <f t="shared" si="2"/>
         <v>0.57564996829422954</v>
       </c>
-      <c r="L54" s="14">
-        <f t="shared" si="2"/>
+      <c r="L54" s="10">
+        <f t="shared" si="3"/>
         <v>9078</v>
       </c>
-      <c r="M54" s="14">
-        <f t="shared" si="3"/>
+      <c r="M54" s="10">
+        <f t="shared" si="4"/>
         <v>72624</v>
       </c>
-      <c r="N54" s="11">
+      <c r="N54" s="7">
         <v>58.9</v>
       </c>
-      <c r="O54" s="11">
+      <c r="O54" s="7">
         <v>56.6</v>
       </c>
-      <c r="P54" s="11">
+      <c r="P54" s="7">
         <v>19</v>
       </c>
-      <c r="Q54" s="11">
+      <c r="Q54" s="7">
         <v>700</v>
       </c>
     </row>
@@ -3868,56 +3868,56 @@
       <c r="A55" s="3">
         <v>52</v>
       </c>
-      <c r="B55" s="17" t="s">
+      <c r="B55" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C55" s="21" t="s">
+      <c r="C55" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="D55" s="15">
+      <c r="D55" s="11">
         <v>8</v>
       </c>
-      <c r="E55" s="15">
+      <c r="E55" s="11">
         <v>2.87</v>
       </c>
-      <c r="F55" s="15">
+      <c r="F55" s="11">
         <v>4362</v>
       </c>
-      <c r="G55" s="15">
+      <c r="G55" s="11">
         <v>2330</v>
       </c>
-      <c r="H55" s="15">
-        <v>0</v>
-      </c>
-      <c r="I55" s="12">
-        <f t="shared" si="0"/>
+      <c r="H55" s="11">
+        <v>0</v>
+      </c>
+      <c r="I55" s="8">
+        <f t="shared" si="1"/>
         <v>6692</v>
       </c>
-      <c r="J55" s="13">
+      <c r="J55" s="9">
         <v>17700</v>
       </c>
-      <c r="K55" s="10">
-        <f t="shared" si="1"/>
+      <c r="K55" s="6">
+        <f t="shared" si="2"/>
         <v>0.62192090395480226</v>
       </c>
-      <c r="L55" s="14">
-        <f t="shared" si="2"/>
+      <c r="L55" s="10">
+        <f t="shared" si="3"/>
         <v>11008</v>
       </c>
-      <c r="M55" s="14">
-        <f t="shared" si="3"/>
+      <c r="M55" s="10">
+        <f t="shared" si="4"/>
         <v>88064</v>
       </c>
-      <c r="N55" s="15">
+      <c r="N55" s="11">
         <v>58.9</v>
       </c>
-      <c r="O55" s="15">
+      <c r="O55" s="11">
         <v>56.6</v>
       </c>
-      <c r="P55" s="15">
+      <c r="P55" s="11">
         <v>19</v>
       </c>
-      <c r="Q55" s="15">
+      <c r="Q55" s="11">
         <v>700</v>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       <c r="A56" s="2">
         <v>53</v>
       </c>
-      <c r="B56" s="16" t="s">
+      <c r="B56" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C56" s="21" t="s">
+      <c r="C56" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="7">
         <v>10</v>
       </c>
-      <c r="E56" s="11">
+      <c r="E56" s="7">
         <v>1.62</v>
       </c>
-      <c r="F56" s="15">
+      <c r="F56" s="11">
         <f>1520*E56</f>
         <v>2462.4</v>
       </c>
-      <c r="G56" s="11">
+      <c r="G56" s="7">
         <v>1632</v>
       </c>
-      <c r="H56" s="11">
-        <v>0</v>
-      </c>
-      <c r="I56" s="12">
-        <f t="shared" si="0"/>
+      <c r="H56" s="7">
+        <v>0</v>
+      </c>
+      <c r="I56" s="8">
+        <f t="shared" si="1"/>
         <v>4094.4</v>
       </c>
-      <c r="J56" s="13">
+      <c r="J56" s="9">
         <v>10290</v>
       </c>
-      <c r="K56" s="10">
-        <f t="shared" si="1"/>
+      <c r="K56" s="6">
+        <f t="shared" si="2"/>
         <v>0.60209912536443155</v>
       </c>
-      <c r="L56" s="14">
-        <f t="shared" si="2"/>
+      <c r="L56" s="10">
+        <f t="shared" si="3"/>
         <v>6195.6</v>
       </c>
-      <c r="M56" s="14">
-        <f t="shared" si="3"/>
+      <c r="M56" s="10">
+        <f t="shared" si="4"/>
         <v>61956</v>
       </c>
-      <c r="N56" s="11">
+      <c r="N56" s="7">
         <v>61.3</v>
       </c>
-      <c r="O56" s="11">
+      <c r="O56" s="7">
         <v>59.1</v>
       </c>
-      <c r="P56" s="11">
+      <c r="P56" s="7">
         <v>6</v>
       </c>
-      <c r="Q56" s="11">
+      <c r="Q56" s="7">
         <v>350</v>
       </c>
     </row>
@@ -3983,57 +3983,57 @@
       <c r="A57" s="3">
         <v>54</v>
       </c>
-      <c r="B57" s="20" t="s">
+      <c r="B57" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="C57" s="21" t="s">
+      <c r="C57" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D57" s="15">
+      <c r="D57" s="11">
         <v>12</v>
       </c>
-      <c r="E57" s="15">
+      <c r="E57" s="11">
         <v>0.85</v>
       </c>
-      <c r="F57" s="15">
+      <c r="F57" s="11">
         <f>1520*E57</f>
         <v>1292</v>
       </c>
-      <c r="G57" s="15">
+      <c r="G57" s="11">
         <v>1599</v>
       </c>
-      <c r="H57" s="15">
-        <v>0</v>
-      </c>
-      <c r="I57" s="12">
-        <f t="shared" si="0"/>
+      <c r="H57" s="11">
+        <v>0</v>
+      </c>
+      <c r="I57" s="8">
+        <f t="shared" si="1"/>
         <v>2891</v>
       </c>
-      <c r="J57" s="13">
+      <c r="J57" s="9">
         <v>8600</v>
       </c>
-      <c r="K57" s="10">
-        <f t="shared" si="1"/>
+      <c r="K57" s="6">
+        <f t="shared" si="2"/>
         <v>0.66383720930232559</v>
       </c>
-      <c r="L57" s="14">
-        <f t="shared" si="2"/>
+      <c r="L57" s="10">
+        <f t="shared" si="3"/>
         <v>5709</v>
       </c>
-      <c r="M57" s="14">
-        <f t="shared" si="3"/>
+      <c r="M57" s="10">
+        <f t="shared" si="4"/>
         <v>68508</v>
       </c>
-      <c r="N57" s="15">
+      <c r="N57" s="11">
         <v>56</v>
       </c>
-      <c r="O57" s="15">
+      <c r="O57" s="11">
         <v>53.6</v>
       </c>
-      <c r="P57" s="15">
+      <c r="P57" s="11">
         <v>8</v>
       </c>
-      <c r="Q57" s="15">
+      <c r="Q57" s="11">
         <v>600</v>
       </c>
     </row>
@@ -4041,56 +4041,56 @@
       <c r="A58" s="2">
         <v>55</v>
       </c>
-      <c r="B58" s="19" t="s">
+      <c r="B58" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C58" s="21" t="s">
+      <c r="C58" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="7">
         <v>8</v>
       </c>
-      <c r="E58" s="11">
+      <c r="E58" s="7">
         <v>1.27</v>
       </c>
-      <c r="F58" s="11">
+      <c r="F58" s="7">
         <v>1930</v>
       </c>
-      <c r="G58" s="11">
+      <c r="G58" s="7">
         <v>1648</v>
       </c>
-      <c r="H58" s="11">
-        <v>0</v>
-      </c>
-      <c r="I58" s="12">
-        <f t="shared" si="0"/>
+      <c r="H58" s="7">
+        <v>0</v>
+      </c>
+      <c r="I58" s="8">
+        <f t="shared" si="1"/>
         <v>3578</v>
       </c>
-      <c r="J58" s="13">
+      <c r="J58" s="9">
         <v>12300</v>
       </c>
-      <c r="K58" s="10">
-        <f t="shared" si="1"/>
+      <c r="K58" s="6">
+        <f t="shared" si="2"/>
         <v>0.70910569105691057</v>
       </c>
-      <c r="L58" s="14">
-        <f t="shared" si="2"/>
+      <c r="L58" s="10">
+        <f t="shared" si="3"/>
         <v>8722</v>
       </c>
-      <c r="M58" s="14">
-        <f t="shared" si="3"/>
+      <c r="M58" s="10">
+        <f t="shared" si="4"/>
         <v>69776</v>
       </c>
-      <c r="N58" s="11">
+      <c r="N58" s="7">
         <v>56.2</v>
       </c>
-      <c r="O58" s="11">
+      <c r="O58" s="7">
         <v>53.8</v>
       </c>
-      <c r="P58" s="11">
+      <c r="P58" s="7">
         <v>10</v>
       </c>
-      <c r="Q58" s="11">
+      <c r="Q58" s="7">
         <v>300</v>
       </c>
     </row>
@@ -4098,56 +4098,56 @@
       <c r="A59" s="3">
         <v>56</v>
       </c>
-      <c r="B59" s="17" t="s">
+      <c r="B59" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C59" s="21" t="s">
+      <c r="C59" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D59" s="15">
+      <c r="D59" s="11">
         <v>10</v>
       </c>
-      <c r="E59" s="15">
+      <c r="E59" s="11">
         <v>0.92</v>
       </c>
-      <c r="F59" s="15">
+      <c r="F59" s="11">
         <v>1392</v>
       </c>
-      <c r="G59" s="15">
+      <c r="G59" s="11">
         <v>2412</v>
       </c>
-      <c r="H59" s="15">
-        <v>0</v>
-      </c>
-      <c r="I59" s="12">
-        <f t="shared" si="0"/>
+      <c r="H59" s="11">
+        <v>0</v>
+      </c>
+      <c r="I59" s="8">
+        <f t="shared" si="1"/>
         <v>3804</v>
       </c>
-      <c r="J59" s="13">
+      <c r="J59" s="9">
         <v>10800</v>
       </c>
-      <c r="K59" s="10">
-        <f t="shared" si="1"/>
+      <c r="K59" s="6">
+        <f t="shared" si="2"/>
         <v>0.64777777777777779</v>
       </c>
-      <c r="L59" s="14">
-        <f t="shared" si="2"/>
+      <c r="L59" s="10">
+        <f t="shared" si="3"/>
         <v>6996</v>
       </c>
-      <c r="M59" s="14">
-        <f t="shared" si="3"/>
+      <c r="M59" s="10">
+        <f t="shared" si="4"/>
         <v>69960</v>
       </c>
-      <c r="N59" s="15">
+      <c r="N59" s="11">
         <v>53.1</v>
       </c>
-      <c r="O59" s="15">
+      <c r="O59" s="11">
         <v>50.5</v>
       </c>
-      <c r="P59" s="15">
+      <c r="P59" s="11">
         <v>10</v>
       </c>
-      <c r="Q59" s="15">
+      <c r="Q59" s="11">
         <v>800</v>
       </c>
     </row>
@@ -4155,56 +4155,56 @@
       <c r="A60" s="2">
         <v>57</v>
       </c>
-      <c r="B60" s="16" t="s">
+      <c r="B60" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C60" s="21" t="s">
+      <c r="C60" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D60" s="11">
+      <c r="D60" s="7">
         <v>6</v>
       </c>
-      <c r="E60" s="11">
+      <c r="E60" s="7">
         <v>1.1299999999999999</v>
       </c>
-      <c r="F60" s="11">
+      <c r="F60" s="7">
         <v>1713</v>
       </c>
-      <c r="G60" s="11">
+      <c r="G60" s="7">
         <v>2574</v>
       </c>
-      <c r="H60" s="11">
-        <v>0</v>
-      </c>
-      <c r="I60" s="12">
-        <f t="shared" si="0"/>
+      <c r="H60" s="7">
+        <v>0</v>
+      </c>
+      <c r="I60" s="8">
+        <f t="shared" si="1"/>
         <v>4287</v>
       </c>
-      <c r="J60" s="13">
+      <c r="J60" s="9">
         <v>12300</v>
       </c>
-      <c r="K60" s="10">
-        <f t="shared" si="1"/>
+      <c r="K60" s="6">
+        <f t="shared" si="2"/>
         <v>0.65146341463414636</v>
       </c>
-      <c r="L60" s="14">
-        <f t="shared" si="2"/>
+      <c r="L60" s="10">
+        <f t="shared" si="3"/>
         <v>8013</v>
       </c>
-      <c r="M60" s="14">
-        <f t="shared" si="3"/>
+      <c r="M60" s="10">
+        <f t="shared" si="4"/>
         <v>48078</v>
       </c>
-      <c r="N60" s="11">
+      <c r="N60" s="7">
         <v>54.7</v>
       </c>
-      <c r="O60" s="11">
+      <c r="O60" s="7">
         <v>52.2</v>
       </c>
-      <c r="P60" s="11">
+      <c r="P60" s="7">
         <v>12</v>
       </c>
-      <c r="Q60" s="11">
+      <c r="Q60" s="7">
         <v>300</v>
       </c>
     </row>
@@ -4212,56 +4212,56 @@
       <c r="A61" s="3">
         <v>58</v>
       </c>
-      <c r="B61" s="17" t="s">
+      <c r="B61" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C61" s="21" t="s">
+      <c r="C61" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D61" s="15">
+      <c r="D61" s="11">
         <v>10</v>
       </c>
-      <c r="E61" s="15">
+      <c r="E61" s="11">
         <v>0.2</v>
       </c>
-      <c r="F61" s="15">
+      <c r="F61" s="11">
         <v>304</v>
       </c>
-      <c r="G61" s="15">
+      <c r="G61" s="11">
         <v>2347</v>
       </c>
-      <c r="H61" s="15">
-        <v>0</v>
-      </c>
-      <c r="I61" s="12">
-        <f t="shared" si="0"/>
+      <c r="H61" s="11">
+        <v>0</v>
+      </c>
+      <c r="I61" s="8">
+        <f t="shared" si="1"/>
         <v>2651</v>
       </c>
-      <c r="J61" s="13">
+      <c r="J61" s="9">
         <v>8650</v>
       </c>
-      <c r="K61" s="10">
-        <f t="shared" si="1"/>
+      <c r="K61" s="6">
+        <f t="shared" si="2"/>
         <v>0.6935260115606936</v>
       </c>
-      <c r="L61" s="14">
-        <f t="shared" si="2"/>
+      <c r="L61" s="10">
+        <f t="shared" si="3"/>
         <v>5999</v>
       </c>
-      <c r="M61" s="14">
-        <f t="shared" si="3"/>
+      <c r="M61" s="10">
+        <f t="shared" si="4"/>
         <v>59990</v>
       </c>
-      <c r="N61" s="15">
+      <c r="N61" s="11">
         <v>63.9</v>
       </c>
-      <c r="O61" s="15">
+      <c r="O61" s="11">
         <v>61.9</v>
       </c>
-      <c r="P61" s="15">
+      <c r="P61" s="11">
         <v>10</v>
       </c>
-      <c r="Q61" s="15">
+      <c r="Q61" s="11">
         <v>650</v>
       </c>
     </row>
@@ -4269,56 +4269,56 @@
       <c r="A62" s="2">
         <v>59</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="B62" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C62" s="21" t="s">
+      <c r="C62" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D62" s="11">
+      <c r="D62" s="7">
         <v>5</v>
       </c>
-      <c r="E62" s="11">
+      <c r="E62" s="7">
         <v>0.87</v>
       </c>
-      <c r="F62" s="11">
+      <c r="F62" s="7">
         <v>1322</v>
       </c>
-      <c r="G62" s="11">
+      <c r="G62" s="7">
         <v>2428</v>
       </c>
-      <c r="H62" s="11">
-        <v>0</v>
-      </c>
-      <c r="I62" s="12">
-        <f t="shared" si="0"/>
+      <c r="H62" s="7">
+        <v>0</v>
+      </c>
+      <c r="I62" s="8">
+        <f t="shared" si="1"/>
         <v>3750</v>
       </c>
-      <c r="J62" s="13">
+      <c r="J62" s="9">
         <v>8750</v>
       </c>
-      <c r="K62" s="10">
-        <f t="shared" si="1"/>
+      <c r="K62" s="6">
+        <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
-      <c r="L62" s="14">
-        <f t="shared" si="2"/>
+      <c r="L62" s="10">
+        <f t="shared" si="3"/>
         <v>5000</v>
       </c>
-      <c r="M62" s="14">
-        <f t="shared" si="3"/>
+      <c r="M62" s="10">
+        <f t="shared" si="4"/>
         <v>25000</v>
       </c>
-      <c r="N62" s="11">
+      <c r="N62" s="7">
         <v>63.6</v>
       </c>
-      <c r="O62" s="11">
+      <c r="O62" s="7">
         <v>61.6</v>
       </c>
-      <c r="P62" s="11">
+      <c r="P62" s="7">
         <v>13</v>
       </c>
-      <c r="Q62" s="11">
+      <c r="Q62" s="7">
         <v>750</v>
       </c>
     </row>
@@ -4326,56 +4326,56 @@
       <c r="A63" s="3">
         <v>60</v>
       </c>
-      <c r="B63" s="17" t="s">
+      <c r="B63" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C63" s="21" t="s">
+      <c r="C63" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D63" s="15">
+      <c r="D63" s="11">
         <v>10</v>
       </c>
-      <c r="E63" s="15">
+      <c r="E63" s="11">
         <v>0.45</v>
       </c>
-      <c r="F63" s="15">
+      <c r="F63" s="11">
         <v>684</v>
       </c>
-      <c r="G63" s="15">
+      <c r="G63" s="11">
         <v>1859</v>
       </c>
-      <c r="H63" s="15">
-        <v>0</v>
-      </c>
-      <c r="I63" s="12">
-        <f t="shared" si="0"/>
+      <c r="H63" s="11">
+        <v>0</v>
+      </c>
+      <c r="I63" s="8">
+        <f t="shared" si="1"/>
         <v>2543</v>
       </c>
-      <c r="J63" s="13">
+      <c r="J63" s="9">
         <v>11250</v>
       </c>
-      <c r="K63" s="10">
-        <f t="shared" si="1"/>
+      <c r="K63" s="6">
+        <f t="shared" si="2"/>
         <v>0.77395555555555551</v>
       </c>
-      <c r="L63" s="14">
-        <f t="shared" si="2"/>
+      <c r="L63" s="10">
+        <f t="shared" si="3"/>
         <v>8707</v>
       </c>
-      <c r="M63" s="14">
-        <f t="shared" si="3"/>
+      <c r="M63" s="10">
+        <f t="shared" si="4"/>
         <v>87070</v>
       </c>
-      <c r="N63" s="15">
+      <c r="N63" s="11">
         <v>69.599999999999994</v>
       </c>
-      <c r="O63" s="15">
+      <c r="O63" s="11">
         <v>67.900000000000006</v>
       </c>
-      <c r="P63" s="15">
+      <c r="P63" s="11">
         <v>11</v>
       </c>
-      <c r="Q63" s="15">
+      <c r="Q63" s="11">
         <v>250</v>
       </c>
     </row>
@@ -4383,56 +4383,56 @@
       <c r="A64" s="2">
         <v>61</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B64" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="C64" s="21" t="s">
+      <c r="C64" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="D64" s="11">
+      <c r="D64" s="7">
         <v>10</v>
       </c>
-      <c r="E64" s="11">
+      <c r="E64" s="7">
         <v>1.06</v>
       </c>
-      <c r="F64" s="11">
+      <c r="F64" s="7">
         <v>1611</v>
       </c>
-      <c r="G64" s="11">
+      <c r="G64" s="7">
         <v>1551</v>
       </c>
-      <c r="H64" s="11">
-        <v>0</v>
-      </c>
-      <c r="I64" s="12">
-        <f t="shared" si="0"/>
+      <c r="H64" s="7">
+        <v>0</v>
+      </c>
+      <c r="I64" s="8">
+        <f t="shared" si="1"/>
         <v>3162</v>
       </c>
-      <c r="J64" s="13">
+      <c r="J64" s="9">
         <v>7850</v>
       </c>
-      <c r="K64" s="10">
-        <f t="shared" si="1"/>
+      <c r="K64" s="6">
+        <f t="shared" si="2"/>
         <v>0.59719745222929932</v>
       </c>
-      <c r="L64" s="14">
-        <f t="shared" si="2"/>
+      <c r="L64" s="10">
+        <f t="shared" si="3"/>
         <v>4688</v>
       </c>
-      <c r="M64" s="14">
-        <f t="shared" si="3"/>
+      <c r="M64" s="10">
+        <f t="shared" si="4"/>
         <v>46880</v>
       </c>
-      <c r="N64" s="11">
+      <c r="N64" s="7">
         <v>58.7</v>
       </c>
-      <c r="O64" s="11">
+      <c r="O64" s="7">
         <v>56.4</v>
       </c>
-      <c r="P64" s="11">
+      <c r="P64" s="7">
         <v>9</v>
       </c>
-      <c r="Q64" s="11">
+      <c r="Q64" s="7">
         <v>850</v>
       </c>
     </row>
@@ -4440,56 +4440,56 @@
       <c r="A65" s="3">
         <v>62</v>
       </c>
-      <c r="B65" s="20" t="s">
+      <c r="B65" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C65" s="21" t="s">
+      <c r="C65" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D65" s="15">
+      <c r="D65" s="11">
         <v>18</v>
       </c>
-      <c r="E65" s="15">
+      <c r="E65" s="11">
         <v>1.23</v>
       </c>
-      <c r="F65" s="15">
+      <c r="F65" s="11">
         <v>1870</v>
       </c>
-      <c r="G65" s="15">
+      <c r="G65" s="11">
         <v>4020</v>
       </c>
-      <c r="H65" s="15">
-        <v>0</v>
-      </c>
-      <c r="I65" s="12">
-        <f t="shared" si="0"/>
+      <c r="H65" s="11">
+        <v>0</v>
+      </c>
+      <c r="I65" s="8">
+        <f t="shared" si="1"/>
         <v>5890</v>
       </c>
-      <c r="J65" s="13">
+      <c r="J65" s="9">
         <v>7650</v>
       </c>
-      <c r="K65" s="10">
-        <f t="shared" si="1"/>
+      <c r="K65" s="6">
+        <f t="shared" si="2"/>
         <v>0.23006535947712417</v>
       </c>
-      <c r="L65" s="14">
-        <f t="shared" si="2"/>
+      <c r="L65" s="10">
+        <f t="shared" si="3"/>
         <v>1760</v>
       </c>
-      <c r="M65" s="14">
-        <f t="shared" si="3"/>
+      <c r="M65" s="10">
+        <f t="shared" si="4"/>
         <v>31680</v>
       </c>
-      <c r="N65" s="15">
+      <c r="N65" s="11">
         <v>54.4</v>
       </c>
-      <c r="O65" s="15">
+      <c r="O65" s="11">
         <v>51.8</v>
       </c>
-      <c r="P65" s="15">
+      <c r="P65" s="11">
         <v>15</v>
       </c>
-      <c r="Q65" s="15">
+      <c r="Q65" s="11">
         <v>900</v>
       </c>
     </row>
@@ -4497,56 +4497,56 @@
       <c r="A66" s="2">
         <v>63</v>
       </c>
-      <c r="B66" s="19" t="s">
+      <c r="B66" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C66" s="21" t="s">
+      <c r="C66" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D66" s="11">
+      <c r="D66" s="7">
         <v>10</v>
       </c>
-      <c r="E66" s="11">
+      <c r="E66" s="7">
         <v>2.39</v>
       </c>
-      <c r="F66" s="11">
+      <c r="F66" s="7">
         <v>3633</v>
       </c>
-      <c r="G66" s="11">
+      <c r="G66" s="7">
         <v>6441</v>
       </c>
-      <c r="H66" s="11">
-        <v>0</v>
-      </c>
-      <c r="I66" s="12">
-        <f t="shared" si="0"/>
+      <c r="H66" s="7">
+        <v>0</v>
+      </c>
+      <c r="I66" s="8">
+        <f t="shared" si="1"/>
         <v>10074</v>
       </c>
-      <c r="J66" s="13">
+      <c r="J66" s="9">
         <v>12300</v>
       </c>
-      <c r="K66" s="10">
-        <f t="shared" si="1"/>
+      <c r="K66" s="6">
+        <f t="shared" si="2"/>
         <v>0.18097560975609756</v>
       </c>
-      <c r="L66" s="14">
-        <f t="shared" si="2"/>
+      <c r="L66" s="10">
+        <f t="shared" si="3"/>
         <v>2226</v>
       </c>
-      <c r="M66" s="14">
-        <f t="shared" si="3"/>
+      <c r="M66" s="10">
+        <f t="shared" si="4"/>
         <v>22260</v>
       </c>
-      <c r="N66" s="11">
+      <c r="N66" s="7">
         <v>22.4</v>
       </c>
-      <c r="O66" s="11">
+      <c r="O66" s="7">
         <v>18.100000000000001</v>
       </c>
-      <c r="P66" s="11">
+      <c r="P66" s="7">
         <v>15</v>
       </c>
-      <c r="Q66" s="11">
+      <c r="Q66" s="7">
         <v>300</v>
       </c>
     </row>
@@ -4554,56 +4554,56 @@
       <c r="A67" s="3">
         <v>64</v>
       </c>
-      <c r="B67" s="17" t="s">
+      <c r="B67" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C67" s="21" t="s">
+      <c r="C67" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D67" s="15">
+      <c r="D67" s="11">
         <v>10</v>
       </c>
-      <c r="E67" s="15">
+      <c r="E67" s="11">
         <v>0.76</v>
       </c>
-      <c r="F67" s="15">
+      <c r="F67" s="11">
         <v>1156</v>
       </c>
-      <c r="G67" s="15">
+      <c r="G67" s="11">
         <v>1906</v>
       </c>
-      <c r="H67" s="15">
-        <v>0</v>
-      </c>
-      <c r="I67" s="12">
-        <f t="shared" si="0"/>
+      <c r="H67" s="11">
+        <v>0</v>
+      </c>
+      <c r="I67" s="8">
+        <f t="shared" si="1"/>
         <v>3062</v>
       </c>
-      <c r="J67" s="13">
+      <c r="J67" s="9">
         <v>5750</v>
       </c>
-      <c r="K67" s="10">
-        <f t="shared" si="1"/>
+      <c r="K67" s="6">
+        <f t="shared" si="2"/>
         <v>0.46747826086956523</v>
       </c>
-      <c r="L67" s="14">
-        <f t="shared" si="2"/>
+      <c r="L67" s="10">
+        <f t="shared" si="3"/>
         <v>2688</v>
       </c>
-      <c r="M67" s="14">
-        <f t="shared" si="3"/>
+      <c r="M67" s="10">
+        <f t="shared" si="4"/>
         <v>26880</v>
       </c>
-      <c r="N67" s="15">
+      <c r="N67" s="11">
         <v>31.1</v>
       </c>
-      <c r="O67" s="15">
+      <c r="O67" s="11">
         <v>27.2</v>
       </c>
-      <c r="P67" s="15">
+      <c r="P67" s="11">
         <v>5</v>
       </c>
-      <c r="Q67" s="15">
+      <c r="Q67" s="11">
         <v>750</v>
       </c>
     </row>
@@ -4611,56 +4611,56 @@
       <c r="A68" s="2">
         <v>65</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="C68" s="21" t="s">
+      <c r="C68" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D68" s="11">
-        <v>2</v>
-      </c>
-      <c r="E68" s="11">
+      <c r="D68" s="7">
+        <v>1</v>
+      </c>
+      <c r="E68" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F68" s="11">
+      <c r="F68" s="7">
         <v>1672</v>
       </c>
-      <c r="G68" s="11">
+      <c r="G68" s="7">
         <v>1534</v>
       </c>
-      <c r="H68" s="11">
-        <v>0</v>
-      </c>
-      <c r="I68" s="12">
-        <f t="shared" si="0"/>
+      <c r="H68" s="7">
+        <v>0</v>
+      </c>
+      <c r="I68" s="8">
+        <f t="shared" si="1"/>
         <v>3206</v>
       </c>
-      <c r="J68" s="13">
-        <v>5900</v>
-      </c>
-      <c r="K68" s="10">
-        <f t="shared" si="1"/>
-        <v>0.45661016949152544</v>
-      </c>
-      <c r="L68" s="14">
-        <f t="shared" si="2"/>
-        <v>2694</v>
-      </c>
-      <c r="M68" s="14">
-        <f t="shared" si="3"/>
-        <v>5388</v>
-      </c>
-      <c r="N68" s="11">
+      <c r="J68" s="9">
+        <v>7000</v>
+      </c>
+      <c r="K68" s="6">
+        <f t="shared" si="2"/>
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="L68" s="10">
+        <f t="shared" si="3"/>
+        <v>3794</v>
+      </c>
+      <c r="M68" s="10">
+        <f t="shared" si="4"/>
+        <v>3794</v>
+      </c>
+      <c r="N68" s="7">
         <v>30.3</v>
       </c>
-      <c r="O68" s="11">
+      <c r="O68" s="7">
         <v>26.4</v>
       </c>
-      <c r="P68" s="11">
+      <c r="P68" s="7">
         <v>5</v>
       </c>
-      <c r="Q68" s="11">
+      <c r="Q68" s="7">
         <v>900</v>
       </c>
     </row>
@@ -4668,81 +4668,81 @@
       <c r="A69" s="3">
         <v>66</v>
       </c>
-      <c r="B69" s="17" t="s">
+      <c r="B69" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C69" s="21" t="s">
+      <c r="C69" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D69" s="15">
+      <c r="D69" s="11">
         <v>2</v>
       </c>
-      <c r="E69" s="15">
-        <v>0</v>
-      </c>
-      <c r="F69" s="15">
-        <v>0</v>
-      </c>
-      <c r="G69" s="15">
+      <c r="E69" s="11">
+        <v>0</v>
+      </c>
+      <c r="F69" s="11">
+        <v>0</v>
+      </c>
+      <c r="G69" s="11">
         <v>1794</v>
       </c>
-      <c r="H69" s="15">
-        <v>0</v>
-      </c>
-      <c r="I69" s="12">
-        <f t="shared" ref="I69" si="5">F69+G69</f>
+      <c r="H69" s="11">
+        <v>0</v>
+      </c>
+      <c r="I69" s="8">
+        <f t="shared" ref="I69" si="6">F69+G69</f>
         <v>1794</v>
       </c>
-      <c r="J69" s="13">
+      <c r="J69" s="9">
         <v>6450</v>
       </c>
-      <c r="K69" s="10">
+      <c r="K69" s="6">
         <f>L69/J69</f>
         <v>0.7218604651162791</v>
       </c>
-      <c r="L69" s="14">
-        <f t="shared" ref="L69" si="6">J69-I69</f>
+      <c r="L69" s="10">
+        <f t="shared" ref="L69" si="7">J69-I69</f>
         <v>4656</v>
       </c>
-      <c r="M69" s="14">
-        <f t="shared" si="3"/>
+      <c r="M69" s="10">
+        <f t="shared" si="4"/>
         <v>9312</v>
       </c>
-      <c r="N69" s="15">
+      <c r="N69" s="11">
         <v>59.2</v>
       </c>
-      <c r="O69" s="15">
+      <c r="O69" s="11">
         <v>57</v>
       </c>
-      <c r="P69" s="15">
+      <c r="P69" s="11">
         <v>6</v>
       </c>
-      <c r="Q69" s="15">
+      <c r="Q69" s="11">
         <v>450</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
+      <c r="A70" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
       <c r="K70" s="4">
         <v>6412350</v>
       </c>
       <c r="L70" s="4">
         <v>49</v>
       </c>
-      <c r="N70" s="9">
+      <c r="N70" s="5">
         <f>SUM(M4:M69)</f>
-        <v>3253191</v>
+        <v>3346021</v>
       </c>
     </row>
   </sheetData>

--- a/AQUAVO_FINAL_v9.xlsx
+++ b/AQUAVO_FINAL_v9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaafa\Desktop\upload\FishWebClean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F35309D-2EFB-40D5-94AA-92FE5EF25290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6A4F46-6F8B-4C9F-92E2-68771D718F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1243,19 +1243,19 @@
         <v>8600</v>
       </c>
       <c r="J8" s="9">
-        <v>14300</v>
+        <v>15500</v>
       </c>
       <c r="K8" s="6">
         <f t="shared" si="2"/>
-        <v>0.39860139860139859</v>
+        <v>0.44516129032258067</v>
       </c>
       <c r="L8" s="10">
         <f t="shared" si="3"/>
-        <v>5700</v>
+        <v>6900</v>
       </c>
       <c r="M8" s="10">
         <f t="shared" si="0"/>
-        <v>28500</v>
+        <v>34500</v>
       </c>
       <c r="N8" s="7">
         <v>13.3</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="N70" s="5">
         <f>SUM(M4:M69)</f>
-        <v>3346021</v>
+        <v>3352021</v>
       </c>
     </row>
   </sheetData>

--- a/AQUAVO_FINAL_v9.xlsx
+++ b/AQUAVO_FINAL_v9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaafa\Desktop\upload\FishWebClean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6A4F46-6F8B-4C9F-92E2-68771D718F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{657668EC-1223-41BC-BB04-AB141203B92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3723,19 +3723,19 @@
         <v>3587</v>
       </c>
       <c r="J52" s="9">
-        <v>6600</v>
+        <v>8000</v>
       </c>
       <c r="K52" s="6">
         <f t="shared" si="2"/>
-        <v>0.45651515151515154</v>
+        <v>0.55162500000000003</v>
       </c>
       <c r="L52" s="10">
         <f t="shared" si="3"/>
-        <v>3013</v>
+        <v>4413</v>
       </c>
       <c r="M52" s="10">
         <f t="shared" si="4"/>
-        <v>45195</v>
+        <v>66195</v>
       </c>
       <c r="N52" s="7">
         <v>54.4</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="N70" s="5">
         <f>SUM(M4:M69)</f>
-        <v>3352021</v>
+        <v>3373021</v>
       </c>
     </row>
   </sheetData>

--- a/AQUAVO_FINAL_v9.xlsx
+++ b/AQUAVO_FINAL_v9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaafa\Desktop\upload\FishWebClean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{657668EC-1223-41BC-BB04-AB141203B92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D757B89F-9740-4374-8820-CDE2E75A7EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -413,7 +413,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -460,6 +460,12 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -490,7 +496,7 @@
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
@@ -543,15 +549,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
@@ -560,6 +557,37 @@
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -889,48 +917,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -2262,292 +2290,292 @@
       <c r="P26" s="7"/>
       <c r="Q26" s="7"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
+    <row r="27" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22">
         <v>24</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="25">
         <v>2</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="25">
         <v>6.28</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="25">
         <v>9548</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="25">
         <v>8132</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="26">
         <v>6188</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="27">
         <f>F27+G27+H27</f>
         <v>23868</v>
       </c>
-      <c r="J27" s="18">
+      <c r="J27" s="28">
         <f>31500+H27</f>
         <v>37688</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="29">
         <f t="shared" si="2"/>
         <v>0.36669496922097217</v>
       </c>
-      <c r="L27" s="10">
+      <c r="L27" s="30">
         <f t="shared" si="3"/>
         <v>13820</v>
       </c>
-      <c r="M27" s="10">
+      <c r="M27" s="30">
         <f t="shared" si="4"/>
         <v>27640</v>
       </c>
-      <c r="N27" s="11">
+      <c r="N27" s="25">
         <v>22.2</v>
       </c>
-      <c r="O27" s="11">
+      <c r="O27" s="25">
         <v>17.899999999999999</v>
       </c>
-      <c r="P27" s="11">
+      <c r="P27" s="25">
         <v>30</v>
       </c>
-      <c r="Q27" s="11">
+      <c r="Q27" s="25">
         <v>550</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+    <row r="28" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22">
         <v>25</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="25">
         <v>2</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="25">
         <v>9.73</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="25">
         <v>14793</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="25">
         <v>12565</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="26">
         <v>8214</v>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="27">
         <f>F28+G28+H28</f>
         <v>35572</v>
       </c>
-      <c r="J28" s="18">
+      <c r="J28" s="28">
         <f>(46250)+H28</f>
         <v>54464</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="29">
         <f t="shared" si="2"/>
         <v>0.34687132784958874</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L28" s="30">
         <f t="shared" si="3"/>
         <v>18892</v>
       </c>
-      <c r="M28" s="10">
+      <c r="M28" s="30">
         <f t="shared" si="4"/>
         <v>37784</v>
       </c>
-      <c r="N28" s="7">
+      <c r="N28" s="25">
         <v>22</v>
       </c>
-      <c r="O28" s="7">
+      <c r="O28" s="25">
         <v>17.7</v>
       </c>
-      <c r="P28" s="7">
+      <c r="P28" s="25">
         <v>46</v>
       </c>
-      <c r="Q28" s="7">
+      <c r="Q28" s="25">
         <v>250</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
+    <row r="29" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22">
         <v>26</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="25">
         <v>2</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="25">
         <v>12.52</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="25">
         <v>19032</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="25">
         <v>16288</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="25">
         <v>7351</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="27">
         <f t="shared" ref="I29" si="5">F29+G29+H29</f>
         <v>42671</v>
       </c>
-      <c r="J29" s="18">
+      <c r="J29" s="28">
         <f>58580+H29</f>
         <v>65931</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="29">
         <f t="shared" si="2"/>
         <v>0.35279307154449346</v>
       </c>
-      <c r="L29" s="10">
+      <c r="L29" s="30">
         <f t="shared" si="3"/>
         <v>23260</v>
       </c>
-      <c r="M29" s="10">
+      <c r="M29" s="30">
         <f t="shared" si="4"/>
         <v>46520</v>
       </c>
-      <c r="N29" s="11">
+      <c r="N29" s="25">
         <v>21.5</v>
       </c>
-      <c r="O29" s="11">
+      <c r="O29" s="25">
         <v>17.2</v>
       </c>
-      <c r="P29" s="11">
+      <c r="P29" s="25">
         <v>58</v>
       </c>
-      <c r="Q29" s="11">
+      <c r="Q29" s="25">
         <v>850</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+    <row r="30" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22">
         <v>27</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="25">
         <v>2</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="25">
         <v>8.59</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="25">
         <v>13059</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="25">
         <v>13097</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H30" s="25">
         <v>5044</v>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="27">
         <f>F30+G30+H30</f>
         <v>31200</v>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="32">
         <f>43400+H30</f>
         <v>48444</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="29">
         <f t="shared" si="2"/>
         <v>0.35595739410453309</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30" s="30">
         <f t="shared" si="3"/>
         <v>17244</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M30" s="30">
         <f t="shared" si="4"/>
         <v>34488</v>
       </c>
-      <c r="N30" s="7">
+      <c r="N30" s="25">
         <v>21.4</v>
       </c>
-      <c r="O30" s="7">
+      <c r="O30" s="25">
         <v>17</v>
       </c>
-      <c r="P30" s="7">
+      <c r="P30" s="25">
         <v>43</v>
       </c>
-      <c r="Q30" s="7">
+      <c r="Q30" s="25">
         <v>400</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
+    <row r="31" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22">
         <v>28</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="25">
         <v>2</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="25">
         <v>11.55</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="25">
         <v>17555</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="25">
         <v>16022</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="25">
         <v>6781</v>
       </c>
-      <c r="I31" s="8">
+      <c r="I31" s="27">
         <f>F31+G31+H31</f>
         <v>40358</v>
       </c>
-      <c r="J31" s="9">
+      <c r="J31" s="32">
         <v>55550</v>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="29">
         <f t="shared" si="2"/>
         <v>0.27348334833483351</v>
       </c>
-      <c r="L31" s="10">
+      <c r="L31" s="30">
         <f t="shared" si="3"/>
         <v>15192</v>
       </c>
-      <c r="M31" s="10">
+      <c r="M31" s="30">
         <f t="shared" si="4"/>
         <v>30384</v>
       </c>
-      <c r="N31" s="11">
+      <c r="N31" s="25">
         <v>21.2</v>
       </c>
-      <c r="O31" s="11">
+      <c r="O31" s="25">
         <v>16.899999999999999</v>
       </c>
-      <c r="P31" s="11">
+      <c r="P31" s="25">
         <v>55</v>
       </c>
-      <c r="Q31" s="11">
+      <c r="Q31" s="25">
         <v>550</v>
       </c>
     </row>
@@ -4523,19 +4551,19 @@
         <v>10074</v>
       </c>
       <c r="J66" s="9">
-        <v>12300</v>
+        <v>12500</v>
       </c>
       <c r="K66" s="6">
         <f t="shared" si="2"/>
-        <v>0.18097560975609756</v>
+        <v>0.19408</v>
       </c>
       <c r="L66" s="10">
         <f t="shared" si="3"/>
-        <v>2226</v>
+        <v>2426</v>
       </c>
       <c r="M66" s="10">
         <f t="shared" si="4"/>
-        <v>22260</v>
+        <v>24260</v>
       </c>
       <c r="N66" s="7">
         <v>22.4</v>
@@ -4722,18 +4750,18 @@
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A70" s="23" t="s">
+      <c r="A70" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B70" s="22"/>
-      <c r="C70" s="22"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
-      <c r="H70" s="22"/>
-      <c r="I70" s="22"/>
-      <c r="J70" s="22"/>
+      <c r="B70" s="19"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="19"/>
+      <c r="E70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="19"/>
+      <c r="H70" s="19"/>
+      <c r="I70" s="19"/>
+      <c r="J70" s="19"/>
       <c r="K70" s="4">
         <v>6412350</v>
       </c>
@@ -4742,7 +4770,7 @@
       </c>
       <c r="N70" s="5">
         <f>SUM(M4:M69)</f>
-        <v>3373021</v>
+        <v>3375021</v>
       </c>
     </row>
   </sheetData>
